--- a/РАБОЧИЙ СТОЛ/расчет ПОКОМ КИ/дв 07,07,26 бррсч пок ки.xlsx
+++ b/РАБОЧИЙ СТОЛ/расчет ПОКОМ КИ/дв 07,07,26 бррсч пок ки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчет ПОКОМ КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62782DEC-C343-4ED0-B93E-B3ED3AF3015D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEE758F1-224C-44F9-8C66-7759551730D6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AC$114</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="181029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="258">
   <si>
     <t>Номенклатура</t>
   </si>
@@ -79,9 +79,6 @@
   </si>
   <si>
     <t>ср нов</t>
-  </si>
-  <si>
-    <t>расчет</t>
   </si>
   <si>
     <t>кон ост</t>
@@ -803,6 +800,12 @@
   <si>
     <t>нужно увеличить продажи!!!</t>
   </si>
+  <si>
+    <t>заказ</t>
+  </si>
+  <si>
+    <t>12,07,</t>
+  </si>
 </sst>
 </file>
 
@@ -848,7 +851,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -889,6 +892,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -925,7 +934,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -944,6 +953,7 @@
     <xf numFmtId="164" fontId="4" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="5" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="1" fillId="8" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Arial10px" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -1285,7 +1295,9 @@
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
+      <c r="Q1" s="1">
+        <v>13</v>
+      </c>
       <c r="R1" s="1"/>
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
@@ -1420,43 +1432,43 @@
         <v>15</v>
       </c>
       <c r="Q3" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="R3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="2" t="s">
+      <c r="S3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S3" s="2" t="s">
+      <c r="T3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T3" s="2" t="s">
+      <c r="U3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AB3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="V3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="W3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="X3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="Y3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="Z3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AA3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AB3" s="2" t="s">
+      <c r="AC3" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="AC3" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="AD3" s="1"/>
       <c r="AE3" s="1"/>
@@ -1495,37 +1507,39 @@
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="P4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="P4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q4" s="1"/>
+      <c r="Q4" s="1" t="s">
+        <v>257</v>
+      </c>
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
       <c r="T4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="U4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="U4" s="1" t="s">
+      <c r="V4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="V4" s="1" t="s">
+      <c r="W4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="W4" s="1" t="s">
+      <c r="X4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="X4" s="1" t="s">
+      <c r="Y4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="Y4" s="1" t="s">
+      <c r="Z4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="Z4" s="1" t="s">
+      <c r="AA4" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="AA4" s="1" t="s">
-        <v>31</v>
       </c>
       <c r="AB4" s="1"/>
       <c r="AC4" s="1"/>
@@ -1593,7 +1607,7 @@
       </c>
       <c r="Q5" s="4">
         <f t="shared" si="0"/>
-        <v>4402.0176000000001</v>
+        <v>8199.4178000000011</v>
       </c>
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
@@ -1632,7 +1646,7 @@
       <c r="AB5" s="1"/>
       <c r="AC5" s="4">
         <f>SUM(AC6:AC497)</f>
-        <v>2425.0986099999996</v>
+        <v>5252</v>
       </c>
       <c r="AD5" s="1"/>
       <c r="AE5" s="1"/>
@@ -1657,10 +1671,10 @@
     </row>
     <row r="6" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>33</v>
       </c>
       <c r="C6" s="1">
         <v>587.149</v>
@@ -1679,7 +1693,7 @@
       </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J6" s="1"/>
       <c r="K6" s="1">
@@ -1730,10 +1744,10 @@
         <v>53.9236</v>
       </c>
       <c r="AB6" s="17" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AC6" s="1">
-        <f t="shared" ref="AC6:AC16" si="6">G6*Q6</f>
+        <f>ROUND(G6*Q6,0)</f>
         <v>0</v>
       </c>
       <c r="AD6" s="1"/>
@@ -1759,10 +1773,10 @@
     </row>
     <row r="7" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C7" s="1">
         <v>708.23099999999999</v>
@@ -1781,7 +1795,7 @@
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J7" s="1"/>
       <c r="K7" s="1">
@@ -1833,7 +1847,7 @@
       </c>
       <c r="AB7" s="1"/>
       <c r="AC7" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="AC7:AC70" si="6">ROUND(G7*Q7,0)</f>
         <v>0</v>
       </c>
       <c r="AD7" s="1"/>
@@ -1859,10 +1873,10 @@
     </row>
     <row r="8" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C8" s="1">
         <v>553.59699999999998</v>
@@ -1881,7 +1895,7 @@
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J8" s="1"/>
       <c r="K8" s="1">
@@ -1959,10 +1973,10 @@
     </row>
     <row r="9" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="C9" s="1">
         <v>1206.607</v>
@@ -1981,7 +1995,7 @@
       </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J9" s="1"/>
       <c r="K9" s="1">
@@ -1998,13 +2012,13 @@
         <f t="shared" si="3"/>
         <v>130.80000000000001</v>
       </c>
-      <c r="Q9" s="5">
-        <f t="shared" ref="Q9" si="7">11*P9-O9-F9</f>
-        <v>285.19300000000021</v>
+      <c r="Q9" s="18">
+        <f>$Q$1*P9-O9-F9</f>
+        <v>546.79300000000012</v>
       </c>
       <c r="R9" s="1">
         <f t="shared" si="4"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="S9" s="1">
         <f t="shared" si="5"/>
@@ -2037,7 +2051,7 @@
       <c r="AB9" s="1"/>
       <c r="AC9" s="1">
         <f t="shared" si="6"/>
-        <v>128.33685000000011</v>
+        <v>246</v>
       </c>
       <c r="AD9" s="1"/>
       <c r="AE9" s="1"/>
@@ -2062,10 +2076,10 @@
     </row>
     <row r="10" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C10" s="1">
         <v>1003</v>
@@ -2084,7 +2098,7 @@
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J10" s="1"/>
       <c r="K10" s="1">
@@ -2103,10 +2117,13 @@
         <f t="shared" si="3"/>
         <v>109</v>
       </c>
-      <c r="Q10" s="5"/>
+      <c r="Q10" s="18">
+        <f>$Q$1*P10-O10-F10</f>
+        <v>172</v>
+      </c>
       <c r="R10" s="1">
         <f t="shared" si="4"/>
-        <v>11.422018348623853</v>
+        <v>13</v>
       </c>
       <c r="S10" s="1">
         <f t="shared" si="5"/>
@@ -2139,7 +2156,7 @@
       <c r="AB10" s="1"/>
       <c r="AC10" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="AD10" s="1"/>
       <c r="AE10" s="1"/>
@@ -2164,10 +2181,10 @@
     </row>
     <row r="11" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C11" s="1">
         <v>261</v>
@@ -2186,7 +2203,7 @@
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J11" s="1"/>
       <c r="K11" s="1">
@@ -2237,7 +2254,7 @@
         <v>18</v>
       </c>
       <c r="AB11" s="17" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AC11" s="1">
         <f t="shared" si="6"/>
@@ -2266,10 +2283,10 @@
     </row>
     <row r="12" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C12" s="1">
         <v>208</v>
@@ -2288,7 +2305,7 @@
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J12" s="1"/>
       <c r="K12" s="1">
@@ -2366,10 +2383,10 @@
     </row>
     <row r="13" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C13" s="1">
         <v>368</v>
@@ -2388,7 +2405,7 @@
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J13" s="1"/>
       <c r="K13" s="1">
@@ -2439,7 +2456,7 @@
         <v>30.4</v>
       </c>
       <c r="AB13" s="17" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AC13" s="1">
         <f t="shared" si="6"/>
@@ -2468,10 +2485,10 @@
     </row>
     <row r="14" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C14" s="1">
         <v>884.92</v>
@@ -2490,7 +2507,7 @@
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J14" s="1"/>
       <c r="K14" s="1">
@@ -2568,10 +2585,10 @@
     </row>
     <row r="15" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C15" s="1">
         <v>2550.1759999999999</v>
@@ -2590,7 +2607,7 @@
       </c>
       <c r="H15" s="1"/>
       <c r="I15" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J15" s="1"/>
       <c r="K15" s="1">
@@ -2670,10 +2687,10 @@
     </row>
     <row r="16" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C16" s="1">
         <v>107.328</v>
@@ -2692,7 +2709,7 @@
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J16" s="1"/>
       <c r="K16" s="1">
@@ -2772,10 +2789,10 @@
     </row>
     <row r="17" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C17" s="9">
         <v>-214.43600000000001</v>
@@ -2794,10 +2811,10 @@
       </c>
       <c r="H17" s="9"/>
       <c r="I17" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="J17" s="9" t="s">
         <v>57</v>
-      </c>
-      <c r="J17" s="9" t="s">
-        <v>58</v>
       </c>
       <c r="K17" s="9">
         <v>193.87200000000001</v>
@@ -2847,9 +2864,12 @@
         <v>223.1756</v>
       </c>
       <c r="AB17" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="AC17" s="9"/>
+        <v>58</v>
+      </c>
+      <c r="AC17" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AD17" s="1"/>
       <c r="AE17" s="1"/>
       <c r="AF17" s="1"/>
@@ -2873,10 +2893,10 @@
     </row>
     <row r="18" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C18" s="1">
         <v>38.877000000000002</v>
@@ -2895,7 +2915,7 @@
       </c>
       <c r="H18" s="1"/>
       <c r="I18" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J18" s="1"/>
       <c r="K18" s="1">
@@ -2949,7 +2969,7 @@
       </c>
       <c r="AB18" s="1"/>
       <c r="AC18" s="1">
-        <f>G18*Q18</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD18" s="1"/>
@@ -2975,10 +2995,10 @@
     </row>
     <row r="19" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C19" s="1">
         <v>56.731999999999999</v>
@@ -2997,7 +3017,7 @@
       </c>
       <c r="H19" s="1"/>
       <c r="I19" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J19" s="1"/>
       <c r="K19" s="1">
@@ -3015,7 +3035,7 @@
         <v>4.0621999999999998</v>
       </c>
       <c r="Q19" s="5">
-        <f t="shared" ref="Q19" si="8">11*P19-O19-F19</f>
+        <f t="shared" ref="Q19" si="7">11*P19-O19-F19</f>
         <v>8.6441999999999979</v>
       </c>
       <c r="R19" s="1">
@@ -3052,8 +3072,8 @@
       </c>
       <c r="AB19" s="1"/>
       <c r="AC19" s="1">
-        <f>G19*Q19</f>
-        <v>8.6441999999999979</v>
+        <f t="shared" si="6"/>
+        <v>9</v>
       </c>
       <c r="AD19" s="1"/>
       <c r="AE19" s="1"/>
@@ -3078,10 +3098,10 @@
     </row>
     <row r="20" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C20" s="1">
         <v>610.38</v>
@@ -3100,7 +3120,7 @@
       </c>
       <c r="H20" s="1"/>
       <c r="I20" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J20" s="1"/>
       <c r="K20" s="1">
@@ -3152,7 +3172,7 @@
       </c>
       <c r="AB20" s="1"/>
       <c r="AC20" s="1">
-        <f>G20*Q20</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD20" s="1"/>
@@ -3178,10 +3198,10 @@
     </row>
     <row r="21" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C21" s="9">
         <v>-30.382000000000001</v>
@@ -3196,10 +3216,10 @@
       </c>
       <c r="H21" s="9"/>
       <c r="I21" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="J21" s="9" t="s">
         <v>67</v>
-      </c>
-      <c r="J21" s="9" t="s">
-        <v>68</v>
       </c>
       <c r="K21" s="9"/>
       <c r="L21" s="9">
@@ -3247,7 +3267,10 @@
         <v>0</v>
       </c>
       <c r="AB21" s="9"/>
-      <c r="AC21" s="9"/>
+      <c r="AC21" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AD21" s="1"/>
       <c r="AE21" s="1"/>
       <c r="AF21" s="1"/>
@@ -3271,10 +3294,10 @@
     </row>
     <row r="22" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C22" s="1">
         <v>197.136</v>
@@ -3293,7 +3316,7 @@
       </c>
       <c r="H22" s="1"/>
       <c r="I22" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J22" s="1"/>
       <c r="K22" s="1">
@@ -3313,7 +3336,7 @@
         <v>26.021800000000002</v>
       </c>
       <c r="Q22" s="5">
-        <f t="shared" ref="Q22:Q85" si="9">11*P22-O22-F22</f>
+        <f t="shared" ref="Q22:Q85" si="8">11*P22-O22-F22</f>
         <v>78.77759999999995</v>
       </c>
       <c r="R22" s="1">
@@ -3350,8 +3373,8 @@
       </c>
       <c r="AB22" s="1"/>
       <c r="AC22" s="1">
-        <f t="shared" ref="AC22:AC53" si="10">G22*Q22</f>
-        <v>78.77759999999995</v>
+        <f t="shared" si="6"/>
+        <v>79</v>
       </c>
       <c r="AD22" s="1"/>
       <c r="AE22" s="1"/>
@@ -3376,10 +3399,10 @@
     </row>
     <row r="23" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C23" s="1">
         <v>317.98</v>
@@ -3398,7 +3421,7 @@
       </c>
       <c r="H23" s="1"/>
       <c r="I23" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J23" s="1"/>
       <c r="K23" s="1">
@@ -3450,7 +3473,7 @@
       </c>
       <c r="AB23" s="1"/>
       <c r="AC23" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD23" s="1"/>
@@ -3476,10 +3499,10 @@
     </row>
     <row r="24" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C24" s="1">
         <v>46.426000000000002</v>
@@ -3498,7 +3521,7 @@
       </c>
       <c r="H24" s="1"/>
       <c r="I24" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J24" s="1"/>
       <c r="K24" s="1">
@@ -3516,7 +3539,7 @@
         <v>4.6448</v>
       </c>
       <c r="Q24" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>28.184799999999996</v>
       </c>
       <c r="R24" s="1">
@@ -3553,8 +3576,8 @@
       </c>
       <c r="AB24" s="1"/>
       <c r="AC24" s="1">
-        <f t="shared" si="10"/>
-        <v>28.184799999999996</v>
+        <f t="shared" si="6"/>
+        <v>28</v>
       </c>
       <c r="AD24" s="1"/>
       <c r="AE24" s="1"/>
@@ -3579,10 +3602,10 @@
     </row>
     <row r="25" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C25" s="1">
         <v>667.375</v>
@@ -3601,7 +3624,7 @@
       </c>
       <c r="H25" s="1"/>
       <c r="I25" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J25" s="1"/>
       <c r="K25" s="1">
@@ -3652,10 +3675,10 @@
         <v>37.685600000000001</v>
       </c>
       <c r="AB25" s="17" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AC25" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD25" s="1"/>
@@ -3681,10 +3704,10 @@
     </row>
     <row r="26" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C26" s="1">
         <v>104.55200000000001</v>
@@ -3703,7 +3726,7 @@
       </c>
       <c r="H26" s="1"/>
       <c r="I26" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J26" s="1"/>
       <c r="K26" s="1">
@@ -3721,7 +3744,7 @@
         <v>34.035199999999996</v>
       </c>
       <c r="Q26" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>171.27119999999994</v>
       </c>
       <c r="R26" s="1">
@@ -3758,8 +3781,8 @@
       </c>
       <c r="AB26" s="1"/>
       <c r="AC26" s="1">
-        <f t="shared" si="10"/>
-        <v>171.27119999999994</v>
+        <f t="shared" si="6"/>
+        <v>171</v>
       </c>
       <c r="AD26" s="1"/>
       <c r="AE26" s="1"/>
@@ -3784,10 +3807,10 @@
     </row>
     <row r="27" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C27" s="1">
         <v>699.20500000000004</v>
@@ -3806,7 +3829,7 @@
       </c>
       <c r="H27" s="1"/>
       <c r="I27" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J27" s="1"/>
       <c r="K27" s="1">
@@ -3859,10 +3882,10 @@
         <v>27.750399999999999</v>
       </c>
       <c r="AB27" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AC27" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>50</v>
       </c>
       <c r="AD27" s="1"/>
@@ -3888,10 +3911,10 @@
     </row>
     <row r="28" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C28" s="1">
         <v>240.84</v>
@@ -3910,7 +3933,7 @@
       </c>
       <c r="H28" s="1"/>
       <c r="I28" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J28" s="1"/>
       <c r="K28" s="1">
@@ -3929,13 +3952,13 @@
         <f t="shared" si="3"/>
         <v>174.52519999999998</v>
       </c>
-      <c r="Q28" s="5">
-        <f t="shared" si="9"/>
-        <v>245.95319999999975</v>
+      <c r="Q28" s="18">
+        <f>$Q$1*P28-O28-F28</f>
+        <v>595.00359999999955</v>
       </c>
       <c r="R28" s="1">
         <f t="shared" si="4"/>
-        <v>11</v>
+        <v>12.999999999999998</v>
       </c>
       <c r="S28" s="1">
         <f t="shared" si="5"/>
@@ -3967,8 +3990,8 @@
       </c>
       <c r="AB28" s="1"/>
       <c r="AC28" s="1">
-        <f t="shared" si="10"/>
-        <v>245.95319999999975</v>
+        <f t="shared" si="6"/>
+        <v>595</v>
       </c>
       <c r="AD28" s="1"/>
       <c r="AE28" s="1"/>
@@ -3993,10 +4016,10 @@
     </row>
     <row r="29" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C29" s="1">
         <v>-7.9000000000000001E-2</v>
@@ -4011,7 +4034,7 @@
       </c>
       <c r="H29" s="1"/>
       <c r="I29" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J29" s="1"/>
       <c r="K29" s="1">
@@ -4065,7 +4088,7 @@
       </c>
       <c r="AB29" s="1"/>
       <c r="AC29" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD29" s="1"/>
@@ -4091,10 +4114,10 @@
     </row>
     <row r="30" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C30" s="1">
         <v>110.97499999999999</v>
@@ -4113,7 +4136,7 @@
       </c>
       <c r="H30" s="1"/>
       <c r="I30" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J30" s="1"/>
       <c r="K30" s="1">
@@ -4167,7 +4190,7 @@
       </c>
       <c r="AB30" s="1"/>
       <c r="AC30" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD30" s="1"/>
@@ -4193,10 +4216,10 @@
     </row>
     <row r="31" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C31" s="1">
         <v>118.94199999999999</v>
@@ -4215,7 +4238,7 @@
       </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J31" s="1"/>
       <c r="K31" s="1">
@@ -4233,7 +4256,7 @@
         <v>24.775200000000002</v>
       </c>
       <c r="Q31" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>41.530199999999979</v>
       </c>
       <c r="R31" s="1">
@@ -4270,8 +4293,8 @@
       </c>
       <c r="AB31" s="1"/>
       <c r="AC31" s="1">
-        <f t="shared" si="10"/>
-        <v>41.530199999999979</v>
+        <f t="shared" si="6"/>
+        <v>42</v>
       </c>
       <c r="AD31" s="1"/>
       <c r="AE31" s="1"/>
@@ -4296,10 +4319,10 @@
     </row>
     <row r="32" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C32" s="1">
         <v>125.806</v>
@@ -4318,7 +4341,7 @@
       </c>
       <c r="H32" s="1"/>
       <c r="I32" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J32" s="1"/>
       <c r="K32" s="1">
@@ -4370,7 +4393,7 @@
       </c>
       <c r="AB32" s="1"/>
       <c r="AC32" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD32" s="1"/>
@@ -4396,10 +4419,10 @@
     </row>
     <row r="33" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C33" s="1">
         <v>2527</v>
@@ -4418,7 +4441,7 @@
       </c>
       <c r="H33" s="1"/>
       <c r="I33" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J33" s="1"/>
       <c r="K33" s="1">
@@ -4435,10 +4458,13 @@
         <f t="shared" si="3"/>
         <v>320.60000000000002</v>
       </c>
-      <c r="Q33" s="5"/>
+      <c r="Q33" s="18">
+        <f t="shared" ref="Q33:Q35" si="9">$Q$1*P33-O33-F33</f>
+        <v>475.80000000000018</v>
+      </c>
       <c r="R33" s="1">
         <f t="shared" si="4"/>
-        <v>11.515907673112913</v>
+        <v>13</v>
       </c>
       <c r="S33" s="1">
         <f t="shared" si="5"/>
@@ -4470,8 +4496,8 @@
       </c>
       <c r="AB33" s="1"/>
       <c r="AC33" s="1">
-        <f t="shared" si="10"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>190</v>
       </c>
       <c r="AD33" s="1"/>
       <c r="AE33" s="1"/>
@@ -4496,10 +4522,10 @@
     </row>
     <row r="34" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C34" s="1">
         <v>317</v>
@@ -4518,7 +4544,7 @@
       </c>
       <c r="H34" s="1"/>
       <c r="I34" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="J34" s="1"/>
       <c r="K34" s="1">
@@ -4537,13 +4563,13 @@
         <f t="shared" si="3"/>
         <v>63.8</v>
       </c>
-      <c r="Q34" s="5">
+      <c r="Q34" s="18">
         <f t="shared" si="9"/>
-        <v>92.299999999999955</v>
+        <v>219.89999999999998</v>
       </c>
       <c r="R34" s="1">
         <f t="shared" si="4"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="S34" s="1">
         <f t="shared" si="5"/>
@@ -4575,8 +4601,8 @@
       </c>
       <c r="AB34" s="1"/>
       <c r="AC34" s="1">
-        <f t="shared" si="10"/>
-        <v>41.534999999999982</v>
+        <f t="shared" si="6"/>
+        <v>99</v>
       </c>
       <c r="AD34" s="1"/>
       <c r="AE34" s="1"/>
@@ -4601,10 +4627,10 @@
     </row>
     <row r="35" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C35" s="1">
         <v>463</v>
@@ -4623,7 +4649,7 @@
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J35" s="1"/>
       <c r="K35" s="1">
@@ -4640,10 +4666,13 @@
         <f t="shared" si="3"/>
         <v>127.8</v>
       </c>
-      <c r="Q35" s="5"/>
+      <c r="Q35" s="18">
+        <f t="shared" si="9"/>
+        <v>217.39999999999986</v>
+      </c>
       <c r="R35" s="1">
         <f t="shared" si="4"/>
-        <v>11.298904538341159</v>
+        <v>13</v>
       </c>
       <c r="S35" s="1">
         <f t="shared" si="5"/>
@@ -4675,8 +4704,8 @@
       </c>
       <c r="AB35" s="1"/>
       <c r="AC35" s="1">
-        <f t="shared" si="10"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>87</v>
       </c>
       <c r="AD35" s="1"/>
       <c r="AE35" s="1"/>
@@ -4701,10 +4730,10 @@
     </row>
     <row r="36" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C36" s="1">
         <v>204</v>
@@ -4723,7 +4752,7 @@
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="J36" s="1"/>
       <c r="K36" s="1">
@@ -4743,7 +4772,7 @@
         <v>21.4</v>
       </c>
       <c r="Q36" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>55.799999999999955</v>
       </c>
       <c r="R36" s="1">
@@ -4780,8 +4809,8 @@
       </c>
       <c r="AB36" s="1"/>
       <c r="AC36" s="1">
-        <f t="shared" si="10"/>
-        <v>22.319999999999983</v>
+        <f t="shared" si="6"/>
+        <v>22</v>
       </c>
       <c r="AD36" s="1"/>
       <c r="AE36" s="1"/>
@@ -4806,10 +4835,10 @@
     </row>
     <row r="37" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C37" s="1">
         <v>15.773999999999999</v>
@@ -4828,7 +4857,7 @@
       </c>
       <c r="H37" s="1"/>
       <c r="I37" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="J37" s="1"/>
       <c r="K37" s="1">
@@ -4880,7 +4909,7 @@
       </c>
       <c r="AB37" s="1"/>
       <c r="AC37" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD37" s="1"/>
@@ -4906,10 +4935,10 @@
     </row>
     <row r="38" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C38" s="1">
         <v>184</v>
@@ -4928,30 +4957,30 @@
       </c>
       <c r="H38" s="1"/>
       <c r="I38" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J38" s="1"/>
       <c r="K38" s="1">
         <v>58</v>
       </c>
       <c r="L38" s="1">
-        <f t="shared" ref="L38:L69" si="11">E38-K38</f>
+        <f t="shared" ref="L38:L69" si="10">E38-K38</f>
         <v>0</v>
       </c>
       <c r="M38" s="1"/>
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
       <c r="P38" s="1">
-        <f t="shared" ref="P38:P69" si="12">E38/5</f>
+        <f t="shared" ref="P38:P69" si="11">E38/5</f>
         <v>11.6</v>
       </c>
       <c r="Q38" s="5"/>
       <c r="R38" s="1">
-        <f t="shared" ref="R38:R69" si="13">(F38+O38+Q38)/P38</f>
+        <f t="shared" ref="R38:R69" si="12">(F38+O38+Q38)/P38</f>
         <v>28.103448275862071</v>
       </c>
       <c r="S38" s="1">
-        <f t="shared" ref="S38:S69" si="14">(F38+O38)/P38</f>
+        <f t="shared" ref="S38:S69" si="13">(F38+O38)/P38</f>
         <v>28.103448275862071</v>
       </c>
       <c r="T38" s="1">
@@ -4979,10 +5008,10 @@
         <v>15.2</v>
       </c>
       <c r="AB38" s="17" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AC38" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD38" s="1"/>
@@ -5008,10 +5037,10 @@
     </row>
     <row r="39" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C39" s="1">
         <v>142</v>
@@ -5030,14 +5059,14 @@
       </c>
       <c r="H39" s="1"/>
       <c r="I39" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J39" s="1"/>
       <c r="K39" s="1">
         <v>142</v>
       </c>
       <c r="L39" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>-5</v>
       </c>
       <c r="M39" s="1"/>
@@ -5046,19 +5075,19 @@
         <v>100</v>
       </c>
       <c r="P39" s="1">
+        <f t="shared" si="11"/>
+        <v>27.4</v>
+      </c>
+      <c r="Q39" s="5">
+        <f t="shared" si="8"/>
+        <v>165.39999999999998</v>
+      </c>
+      <c r="R39" s="1">
         <f t="shared" si="12"/>
-        <v>27.4</v>
-      </c>
-      <c r="Q39" s="5">
-        <f t="shared" si="9"/>
-        <v>165.39999999999998</v>
-      </c>
-      <c r="R39" s="1">
+        <v>11</v>
+      </c>
+      <c r="S39" s="1">
         <f t="shared" si="13"/>
-        <v>11</v>
-      </c>
-      <c r="S39" s="1">
-        <f t="shared" si="14"/>
         <v>4.9635036496350367</v>
       </c>
       <c r="T39" s="1">
@@ -5087,8 +5116,8 @@
       </c>
       <c r="AB39" s="1"/>
       <c r="AC39" s="1">
-        <f t="shared" si="10"/>
-        <v>57.889999999999986</v>
+        <f t="shared" si="6"/>
+        <v>58</v>
       </c>
       <c r="AD39" s="1"/>
       <c r="AE39" s="1"/>
@@ -5113,10 +5142,10 @@
     </row>
     <row r="40" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C40" s="1">
         <v>-0.23499999999999999</v>
@@ -5135,32 +5164,32 @@
       </c>
       <c r="H40" s="1"/>
       <c r="I40" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J40" s="1"/>
       <c r="K40" s="1">
         <v>3</v>
       </c>
       <c r="L40" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>-14.601000000000001</v>
       </c>
       <c r="M40" s="1"/>
       <c r="N40" s="1"/>
       <c r="O40" s="1"/>
       <c r="P40" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>-2.3202000000000003</v>
       </c>
       <c r="Q40" s="5"/>
       <c r="R40" s="1">
+        <f t="shared" si="12"/>
+        <v>-29.231962761830872</v>
+      </c>
+      <c r="S40" s="1">
         <f t="shared" si="13"/>
         <v>-29.231962761830872</v>
       </c>
-      <c r="S40" s="1">
-        <f t="shared" si="14"/>
-        <v>-29.231962761830872</v>
-      </c>
       <c r="T40" s="1">
         <v>4.6399999999999997</v>
       </c>
@@ -5187,7 +5216,7 @@
       </c>
       <c r="AB40" s="1"/>
       <c r="AC40" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD40" s="1"/>
@@ -5213,10 +5242,10 @@
     </row>
     <row r="41" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C41" s="1">
         <v>74</v>
@@ -5240,7 +5269,7 @@
         <v>37</v>
       </c>
       <c r="L41" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="M41" s="1"/>
@@ -5249,18 +5278,18 @@
         <v>15.19999999999999</v>
       </c>
       <c r="P41" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>7.4</v>
       </c>
       <c r="Q41" s="5"/>
       <c r="R41" s="1">
+        <f t="shared" si="12"/>
+        <v>13.810810810810809</v>
+      </c>
+      <c r="S41" s="1">
         <f t="shared" si="13"/>
         <v>13.810810810810809</v>
       </c>
-      <c r="S41" s="1">
-        <f t="shared" si="14"/>
-        <v>13.810810810810809</v>
-      </c>
       <c r="T41" s="1">
         <v>10</v>
       </c>
@@ -5287,7 +5316,7 @@
       </c>
       <c r="AB41" s="1"/>
       <c r="AC41" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD41" s="1"/>
@@ -5313,10 +5342,10 @@
     </row>
     <row r="42" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C42" s="1">
         <v>163</v>
@@ -5335,32 +5364,32 @@
       </c>
       <c r="H42" s="1"/>
       <c r="I42" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="J42" s="1"/>
       <c r="K42" s="1">
         <v>192</v>
       </c>
       <c r="L42" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>-75</v>
       </c>
       <c r="M42" s="1"/>
       <c r="N42" s="1"/>
       <c r="O42" s="1"/>
       <c r="P42" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>23.4</v>
       </c>
       <c r="Q42" s="5"/>
       <c r="R42" s="1">
+        <f t="shared" si="12"/>
+        <v>19.82905982905983</v>
+      </c>
+      <c r="S42" s="1">
         <f t="shared" si="13"/>
         <v>19.82905982905983</v>
       </c>
-      <c r="S42" s="1">
-        <f t="shared" si="14"/>
-        <v>19.82905982905983</v>
-      </c>
       <c r="T42" s="1">
         <v>28.8</v>
       </c>
@@ -5386,10 +5415,10 @@
         <v>5.2</v>
       </c>
       <c r="AB42" s="17" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AC42" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD42" s="1"/>
@@ -5415,10 +5444,10 @@
     </row>
     <row r="43" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C43" s="1">
         <v>357</v>
@@ -5437,14 +5466,14 @@
       </c>
       <c r="H43" s="1"/>
       <c r="I43" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J43" s="1"/>
       <c r="K43" s="1">
         <v>213</v>
       </c>
       <c r="L43" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>-20</v>
       </c>
       <c r="M43" s="1"/>
@@ -5453,19 +5482,19 @@
         <v>77.799999999999955</v>
       </c>
       <c r="P43" s="1">
+        <f t="shared" si="11"/>
+        <v>38.6</v>
+      </c>
+      <c r="Q43" s="5">
+        <f t="shared" si="8"/>
+        <v>129.80000000000007</v>
+      </c>
+      <c r="R43" s="1">
         <f t="shared" si="12"/>
-        <v>38.6</v>
-      </c>
-      <c r="Q43" s="5">
-        <f t="shared" si="9"/>
-        <v>129.80000000000007</v>
-      </c>
-      <c r="R43" s="1">
+        <v>11</v>
+      </c>
+      <c r="S43" s="1">
         <f t="shared" si="13"/>
-        <v>11</v>
-      </c>
-      <c r="S43" s="1">
-        <f t="shared" si="14"/>
         <v>7.637305699481864</v>
       </c>
       <c r="T43" s="1">
@@ -5494,8 +5523,8 @@
       </c>
       <c r="AB43" s="1"/>
       <c r="AC43" s="1">
-        <f t="shared" si="10"/>
-        <v>51.92000000000003</v>
+        <f t="shared" si="6"/>
+        <v>52</v>
       </c>
       <c r="AD43" s="1"/>
       <c r="AE43" s="1"/>
@@ -5520,10 +5549,10 @@
     </row>
     <row r="44" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C44" s="1">
         <v>260.44200000000001</v>
@@ -5542,32 +5571,32 @@
       </c>
       <c r="H44" s="1"/>
       <c r="I44" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J44" s="1"/>
       <c r="K44" s="1">
         <v>130.6</v>
       </c>
       <c r="L44" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>-17.759999999999991</v>
       </c>
       <c r="M44" s="1"/>
       <c r="N44" s="1"/>
       <c r="O44" s="1"/>
       <c r="P44" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>22.568000000000001</v>
       </c>
       <c r="Q44" s="5"/>
       <c r="R44" s="1">
+        <f t="shared" si="12"/>
+        <v>11.318060971286776</v>
+      </c>
+      <c r="S44" s="1">
         <f t="shared" si="13"/>
         <v>11.318060971286776</v>
       </c>
-      <c r="S44" s="1">
-        <f t="shared" si="14"/>
-        <v>11.318060971286776</v>
-      </c>
       <c r="T44" s="1">
         <v>21.9788</v>
       </c>
@@ -5594,7 +5623,7 @@
       </c>
       <c r="AB44" s="1"/>
       <c r="AC44" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD44" s="1"/>
@@ -5620,10 +5649,10 @@
     </row>
     <row r="45" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C45" s="1">
         <v>513</v>
@@ -5642,33 +5671,33 @@
       </c>
       <c r="H45" s="1"/>
       <c r="I45" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J45" s="1"/>
       <c r="K45" s="1">
         <v>275</v>
       </c>
       <c r="L45" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>-10</v>
       </c>
       <c r="M45" s="1"/>
       <c r="N45" s="1"/>
       <c r="O45" s="1"/>
       <c r="P45" s="1">
+        <f t="shared" si="11"/>
+        <v>53</v>
+      </c>
+      <c r="Q45" s="18">
+        <f t="shared" ref="Q45:Q46" si="14">$Q$1*P45-O45-F45</f>
+        <v>383</v>
+      </c>
+      <c r="R45" s="1">
         <f t="shared" si="12"/>
-        <v>53</v>
-      </c>
-      <c r="Q45" s="5">
-        <f t="shared" si="9"/>
-        <v>277</v>
-      </c>
-      <c r="R45" s="1">
+        <v>13</v>
+      </c>
+      <c r="S45" s="1">
         <f t="shared" si="13"/>
-        <v>11</v>
-      </c>
-      <c r="S45" s="1">
-        <f t="shared" si="14"/>
         <v>5.7735849056603774</v>
       </c>
       <c r="T45" s="1">
@@ -5697,8 +5726,8 @@
       </c>
       <c r="AB45" s="1"/>
       <c r="AC45" s="1">
-        <f t="shared" si="10"/>
-        <v>96.949999999999989</v>
+        <f t="shared" si="6"/>
+        <v>134</v>
       </c>
       <c r="AD45" s="1"/>
       <c r="AE45" s="1"/>
@@ -5723,10 +5752,10 @@
     </row>
     <row r="46" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C46" s="1">
         <v>580.48599999999999</v>
@@ -5745,14 +5774,14 @@
       </c>
       <c r="H46" s="1"/>
       <c r="I46" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J46" s="1"/>
       <c r="K46" s="1">
         <v>386</v>
       </c>
       <c r="L46" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="M46" s="1"/>
@@ -5761,19 +5790,19 @@
         <v>127.94759999999999</v>
       </c>
       <c r="P46" s="1">
+        <f t="shared" si="11"/>
+        <v>77.8</v>
+      </c>
+      <c r="Q46" s="18">
+        <f t="shared" si="14"/>
+        <v>436.96640000000002</v>
+      </c>
+      <c r="R46" s="1">
         <f t="shared" si="12"/>
-        <v>77.8</v>
-      </c>
-      <c r="Q46" s="5">
-        <f t="shared" si="9"/>
-        <v>281.3664</v>
-      </c>
-      <c r="R46" s="1">
+        <v>13</v>
+      </c>
+      <c r="S46" s="1">
         <f t="shared" si="13"/>
-        <v>11</v>
-      </c>
-      <c r="S46" s="1">
-        <f t="shared" si="14"/>
         <v>7.3834652956298195</v>
       </c>
       <c r="T46" s="1">
@@ -5802,8 +5831,8 @@
       </c>
       <c r="AB46" s="1"/>
       <c r="AC46" s="1">
-        <f t="shared" si="10"/>
-        <v>112.54656</v>
+        <f t="shared" si="6"/>
+        <v>175</v>
       </c>
       <c r="AD46" s="1"/>
       <c r="AE46" s="1"/>
@@ -5828,10 +5857,10 @@
     </row>
     <row r="47" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C47" s="1">
         <v>142.804</v>
@@ -5850,32 +5879,32 @@
       </c>
       <c r="H47" s="1"/>
       <c r="I47" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J47" s="1"/>
       <c r="K47" s="1">
         <v>72.2</v>
       </c>
       <c r="L47" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>2.0319999999999965</v>
       </c>
       <c r="M47" s="1"/>
       <c r="N47" s="1"/>
       <c r="O47" s="1"/>
       <c r="P47" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>14.846399999999999</v>
       </c>
       <c r="Q47" s="5"/>
       <c r="R47" s="1">
+        <f t="shared" si="12"/>
+        <v>14.89175827136545</v>
+      </c>
+      <c r="S47" s="1">
         <f t="shared" si="13"/>
         <v>14.89175827136545</v>
       </c>
-      <c r="S47" s="1">
-        <f t="shared" si="14"/>
-        <v>14.89175827136545</v>
-      </c>
       <c r="T47" s="1">
         <v>11.8916</v>
       </c>
@@ -5902,7 +5931,7 @@
       </c>
       <c r="AB47" s="1"/>
       <c r="AC47" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD47" s="1"/>
@@ -5928,10 +5957,10 @@
     </row>
     <row r="48" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C48" s="1">
         <v>447.803</v>
@@ -5950,32 +5979,32 @@
       </c>
       <c r="H48" s="1"/>
       <c r="I48" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J48" s="1"/>
       <c r="K48" s="1">
         <v>118.9</v>
       </c>
       <c r="L48" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>-0.132000000000005</v>
       </c>
       <c r="M48" s="1"/>
       <c r="N48" s="1"/>
       <c r="O48" s="1"/>
       <c r="P48" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>23.753599999999999</v>
       </c>
       <c r="Q48" s="5"/>
       <c r="R48" s="1">
+        <f t="shared" si="12"/>
+        <v>34.328312340024254</v>
+      </c>
+      <c r="S48" s="1">
         <f t="shared" si="13"/>
         <v>34.328312340024254</v>
       </c>
-      <c r="S48" s="1">
-        <f t="shared" si="14"/>
-        <v>34.328312340024254</v>
-      </c>
       <c r="T48" s="1">
         <v>27.530799999999999</v>
       </c>
@@ -6001,10 +6030,10 @@
         <v>30.253799999999998</v>
       </c>
       <c r="AB48" s="17" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AC48" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD48" s="1"/>
@@ -6030,10 +6059,10 @@
     </row>
     <row r="49" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C49" s="1">
         <v>101.26</v>
@@ -6052,14 +6081,14 @@
       </c>
       <c r="H49" s="1"/>
       <c r="I49" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J49" s="1"/>
       <c r="K49" s="1">
         <v>113.8</v>
       </c>
       <c r="L49" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>3.0720000000000027</v>
       </c>
       <c r="M49" s="1"/>
@@ -6068,19 +6097,19 @@
         <v>159.81580000000011</v>
       </c>
       <c r="P49" s="1">
+        <f t="shared" si="11"/>
+        <v>23.374400000000001</v>
+      </c>
+      <c r="Q49" s="5">
+        <f t="shared" si="8"/>
+        <v>33.238599999999906</v>
+      </c>
+      <c r="R49" s="1">
         <f t="shared" si="12"/>
-        <v>23.374400000000001</v>
-      </c>
-      <c r="Q49" s="5">
-        <f t="shared" si="9"/>
-        <v>33.238599999999906</v>
-      </c>
-      <c r="R49" s="1">
+        <v>11</v>
+      </c>
+      <c r="S49" s="1">
         <f t="shared" si="13"/>
-        <v>11</v>
-      </c>
-      <c r="S49" s="1">
-        <f t="shared" si="14"/>
         <v>9.5779913067287321</v>
       </c>
       <c r="T49" s="1">
@@ -6109,8 +6138,8 @@
       </c>
       <c r="AB49" s="1"/>
       <c r="AC49" s="1">
-        <f t="shared" si="10"/>
-        <v>33.238599999999906</v>
+        <f t="shared" si="6"/>
+        <v>33</v>
       </c>
       <c r="AD49" s="1"/>
       <c r="AE49" s="1"/>
@@ -6135,10 +6164,10 @@
     </row>
     <row r="50" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C50" s="1">
         <v>315</v>
@@ -6157,14 +6186,14 @@
       </c>
       <c r="H50" s="1"/>
       <c r="I50" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J50" s="1"/>
       <c r="K50" s="1">
         <v>160</v>
       </c>
       <c r="L50" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="M50" s="1"/>
@@ -6173,19 +6202,19 @@
         <v>48.400000000000027</v>
       </c>
       <c r="P50" s="1">
+        <f t="shared" si="11"/>
+        <v>32</v>
+      </c>
+      <c r="Q50" s="5">
+        <f t="shared" si="8"/>
+        <v>35.599999999999966</v>
+      </c>
+      <c r="R50" s="1">
         <f t="shared" si="12"/>
-        <v>32</v>
-      </c>
-      <c r="Q50" s="5">
-        <f t="shared" si="9"/>
-        <v>35.599999999999966</v>
-      </c>
-      <c r="R50" s="1">
+        <v>11</v>
+      </c>
+      <c r="S50" s="1">
         <f t="shared" si="13"/>
-        <v>11</v>
-      </c>
-      <c r="S50" s="1">
-        <f t="shared" si="14"/>
         <v>9.8875000000000011</v>
       </c>
       <c r="T50" s="1">
@@ -6214,8 +6243,8 @@
       </c>
       <c r="AB50" s="1"/>
       <c r="AC50" s="1">
-        <f t="shared" si="10"/>
-        <v>16.019999999999985</v>
+        <f t="shared" si="6"/>
+        <v>16</v>
       </c>
       <c r="AD50" s="1"/>
       <c r="AE50" s="1"/>
@@ -6240,10 +6269,10 @@
     </row>
     <row r="51" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C51" s="1">
         <v>399</v>
@@ -6262,32 +6291,32 @@
       </c>
       <c r="H51" s="1"/>
       <c r="I51" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="J51" s="1"/>
       <c r="K51" s="1">
         <v>207</v>
       </c>
       <c r="L51" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>-2</v>
       </c>
       <c r="M51" s="1"/>
       <c r="N51" s="1"/>
       <c r="O51" s="1"/>
       <c r="P51" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>41</v>
       </c>
       <c r="Q51" s="5"/>
       <c r="R51" s="1">
+        <f t="shared" si="12"/>
+        <v>14.75609756097561</v>
+      </c>
+      <c r="S51" s="1">
         <f t="shared" si="13"/>
         <v>14.75609756097561</v>
       </c>
-      <c r="S51" s="1">
-        <f t="shared" si="14"/>
-        <v>14.75609756097561</v>
-      </c>
       <c r="T51" s="1">
         <v>59</v>
       </c>
@@ -6314,7 +6343,7 @@
       </c>
       <c r="AB51" s="1"/>
       <c r="AC51" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD51" s="1"/>
@@ -6340,10 +6369,10 @@
     </row>
     <row r="52" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C52" s="1">
         <v>51</v>
@@ -6360,21 +6389,21 @@
       </c>
       <c r="H52" s="1"/>
       <c r="I52" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J52" s="1"/>
       <c r="K52" s="1">
         <v>46</v>
       </c>
       <c r="L52" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>-7</v>
       </c>
       <c r="M52" s="1"/>
       <c r="N52" s="1"/>
       <c r="O52" s="1"/>
       <c r="P52" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>7.8</v>
       </c>
       <c r="Q52" s="5">
@@ -6382,11 +6411,11 @@
         <v>57.4</v>
       </c>
       <c r="R52" s="1">
+        <f t="shared" si="12"/>
+        <v>8</v>
+      </c>
+      <c r="S52" s="1">
         <f t="shared" si="13"/>
-        <v>8</v>
-      </c>
-      <c r="S52" s="1">
-        <f t="shared" si="14"/>
         <v>0.64102564102564108</v>
       </c>
       <c r="T52" s="1">
@@ -6415,8 +6444,8 @@
       </c>
       <c r="AB52" s="1"/>
       <c r="AC52" s="1">
-        <f t="shared" si="10"/>
-        <v>22.96</v>
+        <f t="shared" si="6"/>
+        <v>23</v>
       </c>
       <c r="AD52" s="1"/>
       <c r="AE52" s="1"/>
@@ -6441,10 +6470,10 @@
     </row>
     <row r="53" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C53" s="1">
         <v>117</v>
@@ -6463,33 +6492,33 @@
       </c>
       <c r="H53" s="1"/>
       <c r="I53" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J53" s="1"/>
       <c r="K53" s="1">
         <v>75</v>
       </c>
       <c r="L53" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>-21</v>
       </c>
       <c r="M53" s="1"/>
       <c r="N53" s="1"/>
       <c r="O53" s="1"/>
       <c r="P53" s="1">
+        <f t="shared" si="11"/>
+        <v>10.8</v>
+      </c>
+      <c r="Q53" s="5">
+        <f t="shared" si="8"/>
+        <v>20.800000000000011</v>
+      </c>
+      <c r="R53" s="1">
         <f t="shared" si="12"/>
-        <v>10.8</v>
-      </c>
-      <c r="Q53" s="5">
-        <f t="shared" si="9"/>
-        <v>20.800000000000011</v>
-      </c>
-      <c r="R53" s="1">
+        <v>11</v>
+      </c>
+      <c r="S53" s="1">
         <f t="shared" si="13"/>
-        <v>11</v>
-      </c>
-      <c r="S53" s="1">
-        <f t="shared" si="14"/>
         <v>9.0740740740740726</v>
       </c>
       <c r="T53" s="1">
@@ -6518,8 +6547,8 @@
       </c>
       <c r="AB53" s="1"/>
       <c r="AC53" s="1">
-        <f t="shared" si="10"/>
-        <v>8.3200000000000056</v>
+        <f t="shared" si="6"/>
+        <v>8</v>
       </c>
       <c r="AD53" s="1"/>
       <c r="AE53" s="1"/>
@@ -6544,10 +6573,10 @@
     </row>
     <row r="54" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C54" s="1">
         <v>238.571</v>
@@ -6566,32 +6595,32 @@
       </c>
       <c r="H54" s="1"/>
       <c r="I54" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J54" s="1"/>
       <c r="K54" s="1">
         <v>77.8</v>
       </c>
       <c r="L54" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>-8.5450000000000017</v>
       </c>
       <c r="M54" s="1"/>
       <c r="N54" s="1"/>
       <c r="O54" s="1"/>
       <c r="P54" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>13.850999999999999</v>
       </c>
       <c r="Q54" s="5"/>
       <c r="R54" s="1">
+        <f t="shared" si="12"/>
+        <v>25.232401992635914</v>
+      </c>
+      <c r="S54" s="1">
         <f t="shared" si="13"/>
         <v>25.232401992635914</v>
       </c>
-      <c r="S54" s="1">
-        <f t="shared" si="14"/>
-        <v>25.232401992635914</v>
-      </c>
       <c r="T54" s="1">
         <v>12.593400000000001</v>
       </c>
@@ -6617,10 +6646,10 @@
         <v>16.265599999999999</v>
       </c>
       <c r="AB54" s="17" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AC54" s="1">
-        <f t="shared" ref="AC54:AC85" si="15">G54*Q54</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD54" s="1"/>
@@ -6646,10 +6675,10 @@
     </row>
     <row r="55" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C55" s="1">
         <v>212</v>
@@ -6668,32 +6697,32 @@
       </c>
       <c r="H55" s="1"/>
       <c r="I55" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J55" s="1"/>
       <c r="K55" s="1">
         <v>52</v>
       </c>
       <c r="L55" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="M55" s="1"/>
       <c r="N55" s="1"/>
       <c r="O55" s="1"/>
       <c r="P55" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>10.4</v>
       </c>
       <c r="Q55" s="5"/>
       <c r="R55" s="1">
+        <f t="shared" si="12"/>
+        <v>34.807692307692307</v>
+      </c>
+      <c r="S55" s="1">
         <f t="shared" si="13"/>
         <v>34.807692307692307</v>
       </c>
-      <c r="S55" s="1">
-        <f t="shared" si="14"/>
-        <v>34.807692307692307</v>
-      </c>
       <c r="T55" s="1">
         <v>12.4</v>
       </c>
@@ -6719,10 +6748,10 @@
         <v>17.2</v>
       </c>
       <c r="AB55" s="17" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AC55" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD55" s="1"/>
@@ -6748,10 +6777,10 @@
     </row>
     <row r="56" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C56" s="1">
         <v>260.95699999999999</v>
@@ -6770,32 +6799,32 @@
       </c>
       <c r="H56" s="1"/>
       <c r="I56" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J56" s="1"/>
       <c r="K56" s="1">
         <v>125.5</v>
       </c>
       <c r="L56" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>10.070999999999998</v>
       </c>
       <c r="M56" s="1"/>
       <c r="N56" s="1"/>
       <c r="O56" s="1"/>
       <c r="P56" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>27.1142</v>
       </c>
       <c r="Q56" s="5"/>
       <c r="R56" s="1">
+        <f t="shared" si="12"/>
+        <v>22.714555472778098</v>
+      </c>
+      <c r="S56" s="1">
         <f t="shared" si="13"/>
         <v>22.714555472778098</v>
       </c>
-      <c r="S56" s="1">
-        <f t="shared" si="14"/>
-        <v>22.714555472778098</v>
-      </c>
       <c r="T56" s="1">
         <v>24.8506</v>
       </c>
@@ -6821,10 +6850,10 @@
         <v>29.278199999999998</v>
       </c>
       <c r="AB56" s="17" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AC56" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD56" s="1"/>
@@ -6850,10 +6879,10 @@
     </row>
     <row r="57" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C57" s="1">
         <v>79.462999999999994</v>
@@ -6872,33 +6901,33 @@
       </c>
       <c r="H57" s="1"/>
       <c r="I57" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J57" s="1"/>
       <c r="K57" s="1">
         <v>40.4</v>
       </c>
       <c r="L57" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>2.6730000000000018</v>
       </c>
       <c r="M57" s="1"/>
       <c r="N57" s="1"/>
       <c r="O57" s="1"/>
       <c r="P57" s="1">
+        <f t="shared" si="11"/>
+        <v>8.6145999999999994</v>
+      </c>
+      <c r="Q57" s="5">
+        <f t="shared" si="8"/>
+        <v>22.997599999999991</v>
+      </c>
+      <c r="R57" s="1">
         <f t="shared" si="12"/>
-        <v>8.6145999999999994</v>
-      </c>
-      <c r="Q57" s="5">
-        <f t="shared" si="9"/>
-        <v>22.997599999999991</v>
-      </c>
-      <c r="R57" s="1">
+        <v>11</v>
+      </c>
+      <c r="S57" s="1">
         <f t="shared" si="13"/>
-        <v>11</v>
-      </c>
-      <c r="S57" s="1">
-        <f t="shared" si="14"/>
         <v>8.3303925893251005</v>
       </c>
       <c r="T57" s="1">
@@ -6927,8 +6956,8 @@
       </c>
       <c r="AB57" s="1"/>
       <c r="AC57" s="1">
-        <f t="shared" si="15"/>
-        <v>22.997599999999991</v>
+        <f t="shared" si="6"/>
+        <v>23</v>
       </c>
       <c r="AD57" s="1"/>
       <c r="AE57" s="1"/>
@@ -6953,10 +6982,10 @@
     </row>
     <row r="58" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C58" s="1">
         <v>151</v>
@@ -6975,32 +7004,32 @@
       </c>
       <c r="H58" s="1"/>
       <c r="I58" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J58" s="1"/>
       <c r="K58" s="1">
         <v>52</v>
       </c>
       <c r="L58" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="M58" s="1"/>
       <c r="N58" s="1"/>
       <c r="O58" s="1"/>
       <c r="P58" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>10.4</v>
       </c>
       <c r="Q58" s="5"/>
       <c r="R58" s="1">
+        <f t="shared" si="12"/>
+        <v>29.038461538461537</v>
+      </c>
+      <c r="S58" s="1">
         <f t="shared" si="13"/>
         <v>29.038461538461537</v>
       </c>
-      <c r="S58" s="1">
-        <f t="shared" si="14"/>
-        <v>29.038461538461537</v>
-      </c>
       <c r="T58" s="1">
         <v>2.6</v>
       </c>
@@ -7026,10 +7055,10 @@
         <v>18.8</v>
       </c>
       <c r="AB58" s="17" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AC58" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD58" s="1"/>
@@ -7055,10 +7084,10 @@
     </row>
     <row r="59" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C59" s="1">
         <v>41</v>
@@ -7077,32 +7106,32 @@
       </c>
       <c r="H59" s="1"/>
       <c r="I59" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J59" s="1"/>
       <c r="K59" s="1">
         <v>10</v>
       </c>
       <c r="L59" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>-1</v>
       </c>
       <c r="M59" s="1"/>
       <c r="N59" s="1"/>
       <c r="O59" s="1"/>
       <c r="P59" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>1.8</v>
       </c>
       <c r="Q59" s="5"/>
       <c r="R59" s="1">
+        <f t="shared" si="12"/>
+        <v>19.444444444444443</v>
+      </c>
+      <c r="S59" s="1">
         <f t="shared" si="13"/>
         <v>19.444444444444443</v>
       </c>
-      <c r="S59" s="1">
-        <f t="shared" si="14"/>
-        <v>19.444444444444443</v>
-      </c>
       <c r="T59" s="1">
         <v>3.2</v>
       </c>
@@ -7128,10 +7157,10 @@
         <v>3.2</v>
       </c>
       <c r="AB59" s="16" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AC59" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD59" s="1"/>
@@ -7157,10 +7186,10 @@
     </row>
     <row r="60" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C60" s="1">
         <v>37.57</v>
@@ -7179,14 +7208,14 @@
       </c>
       <c r="H60" s="1"/>
       <c r="I60" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J60" s="1"/>
       <c r="K60" s="1">
         <v>68.400000000000006</v>
       </c>
       <c r="L60" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>-10.796000000000006</v>
       </c>
       <c r="M60" s="1"/>
@@ -7195,19 +7224,19 @@
         <v>4</v>
       </c>
       <c r="P60" s="1">
+        <f t="shared" si="11"/>
+        <v>11.520799999999999</v>
+      </c>
+      <c r="Q60" s="5">
+        <f t="shared" si="8"/>
+        <v>6.5037999999999982</v>
+      </c>
+      <c r="R60" s="1">
         <f t="shared" si="12"/>
-        <v>11.520799999999999</v>
-      </c>
-      <c r="Q60" s="5">
-        <f t="shared" si="9"/>
-        <v>6.5037999999999982</v>
-      </c>
-      <c r="R60" s="1">
+        <v>11</v>
+      </c>
+      <c r="S60" s="1">
         <f t="shared" si="13"/>
-        <v>11</v>
-      </c>
-      <c r="S60" s="1">
-        <f t="shared" si="14"/>
         <v>10.435473231025624</v>
       </c>
       <c r="T60" s="1">
@@ -7236,8 +7265,8 @@
       </c>
       <c r="AB60" s="1"/>
       <c r="AC60" s="1">
-        <f t="shared" si="15"/>
-        <v>6.5037999999999982</v>
+        <f t="shared" si="6"/>
+        <v>7</v>
       </c>
       <c r="AD60" s="1"/>
       <c r="AE60" s="1"/>
@@ -7262,10 +7291,10 @@
     </row>
     <row r="61" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C61" s="1">
         <v>20.652000000000001</v>
@@ -7284,33 +7313,33 @@
       </c>
       <c r="H61" s="1"/>
       <c r="I61" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J61" s="1"/>
       <c r="K61" s="1">
         <v>30.672000000000001</v>
       </c>
       <c r="L61" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>-2.5180000000000007</v>
       </c>
       <c r="M61" s="1"/>
       <c r="N61" s="1"/>
       <c r="O61" s="1"/>
       <c r="P61" s="1">
+        <f t="shared" si="11"/>
+        <v>5.6307999999999998</v>
+      </c>
+      <c r="Q61" s="5">
+        <f t="shared" si="8"/>
+        <v>12.753799999999998</v>
+      </c>
+      <c r="R61" s="1">
         <f t="shared" si="12"/>
-        <v>5.6307999999999998</v>
-      </c>
-      <c r="Q61" s="5">
-        <f t="shared" si="9"/>
-        <v>12.753799999999998</v>
-      </c>
-      <c r="R61" s="1">
+        <v>11</v>
+      </c>
+      <c r="S61" s="1">
         <f t="shared" si="13"/>
-        <v>11</v>
-      </c>
-      <c r="S61" s="1">
-        <f t="shared" si="14"/>
         <v>8.7349932514029991</v>
       </c>
       <c r="T61" s="1">
@@ -7339,8 +7368,8 @@
       </c>
       <c r="AB61" s="1"/>
       <c r="AC61" s="1">
-        <f t="shared" si="15"/>
-        <v>12.753799999999998</v>
+        <f t="shared" si="6"/>
+        <v>13</v>
       </c>
       <c r="AD61" s="1"/>
       <c r="AE61" s="1"/>
@@ -7365,10 +7394,10 @@
     </row>
     <row r="62" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C62" s="1">
         <v>602</v>
@@ -7387,14 +7416,14 @@
       </c>
       <c r="H62" s="1"/>
       <c r="I62" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J62" s="1"/>
       <c r="K62" s="1">
         <v>523</v>
       </c>
       <c r="L62" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="M62" s="1"/>
@@ -7403,7 +7432,7 @@
         <v>89.400000000000091</v>
       </c>
       <c r="P62" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>104.6</v>
       </c>
       <c r="Q62" s="5">
@@ -7411,11 +7440,11 @@
         <v>618.99999999999989</v>
       </c>
       <c r="R62" s="1">
+        <f t="shared" si="12"/>
+        <v>9</v>
+      </c>
+      <c r="S62" s="1">
         <f t="shared" si="13"/>
-        <v>9</v>
-      </c>
-      <c r="S62" s="1">
-        <f t="shared" si="14"/>
         <v>3.0822179732313586</v>
       </c>
       <c r="T62" s="1">
@@ -7444,8 +7473,8 @@
       </c>
       <c r="AB62" s="1"/>
       <c r="AC62" s="1">
-        <f t="shared" si="15"/>
-        <v>247.59999999999997</v>
+        <f t="shared" si="6"/>
+        <v>248</v>
       </c>
       <c r="AD62" s="1"/>
       <c r="AE62" s="1"/>
@@ -7470,10 +7499,10 @@
     </row>
     <row r="63" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C63" s="1">
         <v>429</v>
@@ -7492,33 +7521,33 @@
       </c>
       <c r="H63" s="1"/>
       <c r="I63" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J63" s="1"/>
       <c r="K63" s="1">
         <v>368</v>
       </c>
       <c r="L63" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>-12</v>
       </c>
       <c r="M63" s="1"/>
       <c r="N63" s="1"/>
       <c r="O63" s="1"/>
       <c r="P63" s="1">
+        <f t="shared" si="11"/>
+        <v>71.2</v>
+      </c>
+      <c r="Q63" s="18">
+        <f>$Q$1*P63-O63-F63</f>
+        <v>448.6</v>
+      </c>
+      <c r="R63" s="1">
         <f t="shared" si="12"/>
-        <v>71.2</v>
-      </c>
-      <c r="Q63" s="5">
-        <f t="shared" si="9"/>
-        <v>306.20000000000005</v>
-      </c>
-      <c r="R63" s="1">
+        <v>13</v>
+      </c>
+      <c r="S63" s="1">
         <f t="shared" si="13"/>
-        <v>11</v>
-      </c>
-      <c r="S63" s="1">
-        <f t="shared" si="14"/>
         <v>6.6994382022471903</v>
       </c>
       <c r="T63" s="1">
@@ -7547,8 +7576,8 @@
       </c>
       <c r="AB63" s="1"/>
       <c r="AC63" s="1">
-        <f t="shared" si="15"/>
-        <v>122.48000000000002</v>
+        <f t="shared" si="6"/>
+        <v>179</v>
       </c>
       <c r="AD63" s="1"/>
       <c r="AE63" s="1"/>
@@ -7573,10 +7602,10 @@
     </row>
     <row r="64" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C64" s="1">
         <v>313.50299999999999</v>
@@ -7595,32 +7624,32 @@
       </c>
       <c r="H64" s="1"/>
       <c r="I64" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J64" s="1"/>
       <c r="K64" s="1">
         <v>158.90199999999999</v>
       </c>
       <c r="L64" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>-4.3289999999999793</v>
       </c>
       <c r="M64" s="1"/>
       <c r="N64" s="1"/>
       <c r="O64" s="1"/>
       <c r="P64" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>30.9146</v>
       </c>
       <c r="Q64" s="5"/>
       <c r="R64" s="1">
+        <f t="shared" si="12"/>
+        <v>11.045784192582145</v>
+      </c>
+      <c r="S64" s="1">
         <f t="shared" si="13"/>
         <v>11.045784192582145</v>
       </c>
-      <c r="S64" s="1">
-        <f t="shared" si="14"/>
-        <v>11.045784192582145</v>
-      </c>
       <c r="T64" s="1">
         <v>30.956199999999999</v>
       </c>
@@ -7647,7 +7676,7 @@
       </c>
       <c r="AB64" s="1"/>
       <c r="AC64" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD64" s="1"/>
@@ -7673,10 +7702,10 @@
     </row>
     <row r="65" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C65" s="1">
         <v>207.26</v>
@@ -7695,33 +7724,33 @@
       </c>
       <c r="H65" s="1"/>
       <c r="I65" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J65" s="1"/>
       <c r="K65" s="1">
         <v>182.60300000000001</v>
       </c>
       <c r="L65" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>-5.9390000000000214</v>
       </c>
       <c r="M65" s="1"/>
       <c r="N65" s="1"/>
       <c r="O65" s="1"/>
       <c r="P65" s="1">
+        <f t="shared" si="11"/>
+        <v>35.332799999999999</v>
+      </c>
+      <c r="Q65" s="5">
+        <f t="shared" si="8"/>
+        <v>189.97880000000001</v>
+      </c>
+      <c r="R65" s="1">
         <f t="shared" si="12"/>
-        <v>35.332799999999999</v>
-      </c>
-      <c r="Q65" s="5">
-        <f t="shared" si="9"/>
-        <v>189.97880000000001</v>
-      </c>
-      <c r="R65" s="1">
+        <v>11</v>
+      </c>
+      <c r="S65" s="1">
         <f t="shared" si="13"/>
-        <v>11</v>
-      </c>
-      <c r="S65" s="1">
-        <f t="shared" si="14"/>
         <v>5.6231603495901821</v>
       </c>
       <c r="T65" s="1">
@@ -7750,8 +7779,8 @@
       </c>
       <c r="AB65" s="1"/>
       <c r="AC65" s="1">
-        <f t="shared" si="15"/>
-        <v>189.97880000000001</v>
+        <f t="shared" si="6"/>
+        <v>190</v>
       </c>
       <c r="AD65" s="1"/>
       <c r="AE65" s="1"/>
@@ -7776,10 +7805,10 @@
     </row>
     <row r="66" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C66" s="1">
         <v>638.49400000000003</v>
@@ -7798,14 +7827,14 @@
       </c>
       <c r="H66" s="1"/>
       <c r="I66" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J66" s="1"/>
       <c r="K66" s="1">
         <v>362.98599999999999</v>
       </c>
       <c r="L66" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>9.3550000000000182</v>
       </c>
       <c r="M66" s="1"/>
@@ -7814,18 +7843,21 @@
         <v>328.09519999999992</v>
       </c>
       <c r="P66" s="1">
+        <f t="shared" si="11"/>
+        <v>74.468199999999996</v>
+      </c>
+      <c r="Q66" s="18">
+        <f>$Q$1*P66-O66-F66</f>
+        <v>86.984400000000164</v>
+      </c>
+      <c r="R66" s="1">
         <f t="shared" si="12"/>
-        <v>74.468199999999996</v>
-      </c>
-      <c r="Q66" s="5"/>
-      <c r="R66" s="1">
+        <v>13</v>
+      </c>
+      <c r="S66" s="1">
         <f t="shared" si="13"/>
         <v>11.831925573600541</v>
       </c>
-      <c r="S66" s="1">
-        <f t="shared" si="14"/>
-        <v>11.831925573600541</v>
-      </c>
       <c r="T66" s="1">
         <v>94.776600000000002</v>
       </c>
@@ -7852,8 +7884,8 @@
       </c>
       <c r="AB66" s="1"/>
       <c r="AC66" s="1">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>87</v>
       </c>
       <c r="AD66" s="1"/>
       <c r="AE66" s="1"/>
@@ -7878,10 +7910,10 @@
     </row>
     <row r="67" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C67" s="1">
         <v>219.25299999999999</v>
@@ -7900,32 +7932,32 @@
       </c>
       <c r="H67" s="1"/>
       <c r="I67" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J67" s="1"/>
       <c r="K67" s="1">
         <v>175.18299999999999</v>
       </c>
       <c r="L67" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>-3.2169999999999845</v>
       </c>
       <c r="M67" s="1"/>
       <c r="N67" s="1"/>
       <c r="O67" s="1"/>
       <c r="P67" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>34.3932</v>
       </c>
       <c r="Q67" s="5"/>
       <c r="R67" s="1">
+        <f t="shared" si="12"/>
+        <v>13.412418733935779</v>
+      </c>
+      <c r="S67" s="1">
         <f t="shared" si="13"/>
         <v>13.412418733935779</v>
       </c>
-      <c r="S67" s="1">
-        <f t="shared" si="14"/>
-        <v>13.412418733935779</v>
-      </c>
       <c r="T67" s="1">
         <v>31.567399999999999</v>
       </c>
@@ -7952,7 +7984,7 @@
       </c>
       <c r="AB67" s="1"/>
       <c r="AC67" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD67" s="1"/>
@@ -7978,10 +8010,10 @@
     </row>
     <row r="68" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C68" s="1">
         <v>441.53100000000001</v>
@@ -8000,14 +8032,14 @@
       </c>
       <c r="H68" s="1"/>
       <c r="I68" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="J68" s="1"/>
       <c r="K68" s="1">
         <v>214.9</v>
       </c>
       <c r="L68" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>-15.569999999999993</v>
       </c>
       <c r="M68" s="1"/>
@@ -8016,18 +8048,18 @@
         <v>74.759800000000098</v>
       </c>
       <c r="P68" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>39.866</v>
       </c>
       <c r="Q68" s="5"/>
       <c r="R68" s="1">
+        <f t="shared" si="12"/>
+        <v>13.047980735463806</v>
+      </c>
+      <c r="S68" s="1">
         <f t="shared" si="13"/>
         <v>13.047980735463806</v>
       </c>
-      <c r="S68" s="1">
-        <f t="shared" si="14"/>
-        <v>13.047980735463806</v>
-      </c>
       <c r="T68" s="1">
         <v>52.215400000000002</v>
       </c>
@@ -8054,7 +8086,7 @@
       </c>
       <c r="AB68" s="1"/>
       <c r="AC68" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD68" s="1"/>
@@ -8080,10 +8112,10 @@
     </row>
     <row r="69" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C69" s="1">
         <v>176</v>
@@ -8102,33 +8134,33 @@
       </c>
       <c r="H69" s="1"/>
       <c r="I69" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="J69" s="1"/>
       <c r="K69" s="1">
         <v>90</v>
       </c>
       <c r="L69" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>6</v>
       </c>
       <c r="M69" s="1"/>
       <c r="N69" s="1"/>
       <c r="O69" s="1"/>
       <c r="P69" s="1">
+        <f t="shared" si="11"/>
+        <v>19.2</v>
+      </c>
+      <c r="Q69" s="5">
+        <f t="shared" si="8"/>
+        <v>30.199999999999989</v>
+      </c>
+      <c r="R69" s="1">
         <f t="shared" si="12"/>
-        <v>19.2</v>
-      </c>
-      <c r="Q69" s="5">
-        <f t="shared" si="9"/>
-        <v>30.199999999999989</v>
-      </c>
-      <c r="R69" s="1">
+        <v>11</v>
+      </c>
+      <c r="S69" s="1">
         <f t="shared" si="13"/>
-        <v>11</v>
-      </c>
-      <c r="S69" s="1">
-        <f t="shared" si="14"/>
         <v>9.4270833333333339</v>
       </c>
       <c r="T69" s="1">
@@ -8157,8 +8189,8 @@
       </c>
       <c r="AB69" s="1"/>
       <c r="AC69" s="1">
-        <f t="shared" si="15"/>
-        <v>18.119999999999994</v>
+        <f t="shared" si="6"/>
+        <v>18</v>
       </c>
       <c r="AD69" s="1"/>
       <c r="AE69" s="1"/>
@@ -8183,10 +8215,10 @@
     </row>
     <row r="70" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C70" s="1">
         <v>409</v>
@@ -8205,14 +8237,14 @@
       </c>
       <c r="H70" s="1"/>
       <c r="I70" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J70" s="1"/>
       <c r="K70" s="1">
         <v>149</v>
       </c>
       <c r="L70" s="1">
-        <f t="shared" ref="L70:L101" si="16">E70-K70</f>
+        <f t="shared" ref="L70:L101" si="15">E70-K70</f>
         <v>11</v>
       </c>
       <c r="M70" s="1"/>
@@ -8221,16 +8253,16 @@
         <v>167.6</v>
       </c>
       <c r="P70" s="1">
-        <f t="shared" ref="P70:P101" si="17">E70/5</f>
+        <f t="shared" ref="P70:P101" si="16">E70/5</f>
         <v>32</v>
       </c>
       <c r="Q70" s="5"/>
       <c r="R70" s="1">
-        <f t="shared" ref="R70:R101" si="18">(F70+O70+Q70)/P70</f>
+        <f t="shared" ref="R70:R101" si="17">(F70+O70+Q70)/P70</f>
         <v>13.182625</v>
       </c>
       <c r="S70" s="1">
-        <f t="shared" ref="S70:S101" si="19">(F70+O70)/P70</f>
+        <f t="shared" ref="S70:S101" si="18">(F70+O70)/P70</f>
         <v>13.182625</v>
       </c>
       <c r="T70" s="1">
@@ -8259,7 +8291,7 @@
       </c>
       <c r="AB70" s="1"/>
       <c r="AC70" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD70" s="1"/>
@@ -8285,10 +8317,10 @@
     </row>
     <row r="71" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C71" s="1">
         <v>171</v>
@@ -8307,14 +8339,14 @@
       </c>
       <c r="H71" s="1"/>
       <c r="I71" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J71" s="1"/>
       <c r="K71" s="1">
         <v>119</v>
       </c>
       <c r="L71" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>3</v>
       </c>
       <c r="M71" s="1"/>
@@ -8323,19 +8355,19 @@
         <v>77.600000000000023</v>
       </c>
       <c r="P71" s="1">
+        <f t="shared" si="16"/>
+        <v>24.4</v>
+      </c>
+      <c r="Q71" s="5">
+        <f t="shared" si="8"/>
+        <v>34.799999999999955</v>
+      </c>
+      <c r="R71" s="1">
         <f t="shared" si="17"/>
-        <v>24.4</v>
-      </c>
-      <c r="Q71" s="5">
-        <f t="shared" si="9"/>
-        <v>34.799999999999955</v>
-      </c>
-      <c r="R71" s="1">
+        <v>11</v>
+      </c>
+      <c r="S71" s="1">
         <f t="shared" si="18"/>
-        <v>11</v>
-      </c>
-      <c r="S71" s="1">
-        <f t="shared" si="19"/>
         <v>9.5737704918032804</v>
       </c>
       <c r="T71" s="1">
@@ -8364,8 +8396,8 @@
       </c>
       <c r="AB71" s="1"/>
       <c r="AC71" s="1">
-        <f t="shared" si="15"/>
-        <v>13.919999999999982</v>
+        <f t="shared" ref="AC71:AC114" si="19">ROUND(G71*Q71,0)</f>
+        <v>14</v>
       </c>
       <c r="AD71" s="1"/>
       <c r="AE71" s="1"/>
@@ -8390,10 +8422,10 @@
     </row>
     <row r="72" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C72" s="1">
         <v>313</v>
@@ -8412,14 +8444,14 @@
       </c>
       <c r="H72" s="1"/>
       <c r="I72" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J72" s="1"/>
       <c r="K72" s="1">
         <v>143</v>
       </c>
       <c r="L72" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>5</v>
       </c>
       <c r="M72" s="1"/>
@@ -8428,19 +8460,19 @@
         <v>107.1999999999999</v>
       </c>
       <c r="P72" s="1">
+        <f t="shared" si="16"/>
+        <v>29.6</v>
+      </c>
+      <c r="Q72" s="5">
+        <f t="shared" si="8"/>
+        <v>7.4000000000001194</v>
+      </c>
+      <c r="R72" s="1">
         <f t="shared" si="17"/>
-        <v>29.6</v>
-      </c>
-      <c r="Q72" s="5">
-        <f t="shared" si="9"/>
-        <v>7.4000000000001194</v>
-      </c>
-      <c r="R72" s="1">
+        <v>11</v>
+      </c>
+      <c r="S72" s="1">
         <f t="shared" si="18"/>
-        <v>11</v>
-      </c>
-      <c r="S72" s="1">
-        <f t="shared" si="19"/>
         <v>10.749999999999996</v>
       </c>
       <c r="T72" s="1">
@@ -8469,8 +8501,8 @@
       </c>
       <c r="AB72" s="1"/>
       <c r="AC72" s="1">
-        <f t="shared" si="15"/>
-        <v>2.4420000000000397</v>
+        <f t="shared" si="19"/>
+        <v>2</v>
       </c>
       <c r="AD72" s="1"/>
       <c r="AE72" s="1"/>
@@ -8495,10 +8527,10 @@
     </row>
     <row r="73" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C73" s="1">
         <v>250</v>
@@ -8517,14 +8549,14 @@
       </c>
       <c r="H73" s="1"/>
       <c r="I73" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J73" s="1"/>
       <c r="K73" s="1">
         <v>177</v>
       </c>
       <c r="L73" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>5</v>
       </c>
       <c r="M73" s="1"/>
@@ -8533,19 +8565,19 @@
         <v>36.399999999999977</v>
       </c>
       <c r="P73" s="1">
+        <f t="shared" si="16"/>
+        <v>36.4</v>
+      </c>
+      <c r="Q73" s="5">
+        <f t="shared" si="8"/>
+        <v>193</v>
+      </c>
+      <c r="R73" s="1">
         <f t="shared" si="17"/>
-        <v>36.4</v>
-      </c>
-      <c r="Q73" s="5">
-        <f t="shared" si="9"/>
-        <v>193</v>
-      </c>
-      <c r="R73" s="1">
+        <v>11</v>
+      </c>
+      <c r="S73" s="1">
         <f t="shared" si="18"/>
-        <v>11</v>
-      </c>
-      <c r="S73" s="1">
-        <f t="shared" si="19"/>
         <v>5.6978021978021971</v>
       </c>
       <c r="T73" s="1">
@@ -8574,8 +8606,8 @@
       </c>
       <c r="AB73" s="1"/>
       <c r="AC73" s="1">
-        <f t="shared" si="15"/>
-        <v>67.55</v>
+        <f t="shared" si="19"/>
+        <v>68</v>
       </c>
       <c r="AD73" s="1"/>
       <c r="AE73" s="1"/>
@@ -8600,10 +8632,10 @@
     </row>
     <row r="74" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C74" s="1">
         <v>60</v>
@@ -8622,14 +8654,14 @@
       </c>
       <c r="H74" s="1"/>
       <c r="I74" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J74" s="1"/>
       <c r="K74" s="1">
         <v>71</v>
       </c>
       <c r="L74" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>-2</v>
       </c>
       <c r="M74" s="1"/>
@@ -8638,18 +8670,18 @@
         <v>124.8</v>
       </c>
       <c r="P74" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>13.8</v>
       </c>
       <c r="Q74" s="5"/>
       <c r="R74" s="1">
+        <f t="shared" si="17"/>
+        <v>12.44927536231884</v>
+      </c>
+      <c r="S74" s="1">
         <f t="shared" si="18"/>
         <v>12.44927536231884</v>
       </c>
-      <c r="S74" s="1">
-        <f t="shared" si="19"/>
-        <v>12.44927536231884</v>
-      </c>
       <c r="T74" s="1">
         <v>18.2</v>
       </c>
@@ -8676,7 +8708,7 @@
       </c>
       <c r="AB74" s="1"/>
       <c r="AC74" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AD74" s="1"/>
@@ -8702,10 +8734,10 @@
     </row>
     <row r="75" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C75" s="1">
         <v>91</v>
@@ -8724,33 +8756,33 @@
       </c>
       <c r="H75" s="1"/>
       <c r="I75" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J75" s="1"/>
       <c r="K75" s="1">
         <v>57</v>
       </c>
       <c r="L75" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>-7</v>
       </c>
       <c r="M75" s="1"/>
       <c r="N75" s="1"/>
       <c r="O75" s="1"/>
       <c r="P75" s="1">
+        <f t="shared" si="16"/>
+        <v>10</v>
+      </c>
+      <c r="Q75" s="5">
+        <f t="shared" si="8"/>
+        <v>34</v>
+      </c>
+      <c r="R75" s="1">
         <f t="shared" si="17"/>
-        <v>10</v>
-      </c>
-      <c r="Q75" s="5">
-        <f t="shared" si="9"/>
-        <v>34</v>
-      </c>
-      <c r="R75" s="1">
+        <v>11</v>
+      </c>
+      <c r="S75" s="1">
         <f t="shared" si="18"/>
-        <v>11</v>
-      </c>
-      <c r="S75" s="1">
-        <f t="shared" si="19"/>
         <v>7.6</v>
       </c>
       <c r="T75" s="1">
@@ -8779,8 +8811,8 @@
       </c>
       <c r="AB75" s="1"/>
       <c r="AC75" s="1">
-        <f t="shared" si="15"/>
-        <v>11.22</v>
+        <f t="shared" si="19"/>
+        <v>11</v>
       </c>
       <c r="AD75" s="1"/>
       <c r="AE75" s="1"/>
@@ -8805,10 +8837,10 @@
     </row>
     <row r="76" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C76" s="1">
         <v>64</v>
@@ -8827,32 +8859,32 @@
       </c>
       <c r="H76" s="1"/>
       <c r="I76" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J76" s="1"/>
       <c r="K76" s="1">
         <v>43</v>
       </c>
       <c r="L76" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>2</v>
       </c>
       <c r="M76" s="1"/>
       <c r="N76" s="1"/>
       <c r="O76" s="1"/>
       <c r="P76" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>9</v>
       </c>
       <c r="Q76" s="5"/>
       <c r="R76" s="1">
+        <f t="shared" si="17"/>
+        <v>11.182666666666668</v>
+      </c>
+      <c r="S76" s="1">
         <f t="shared" si="18"/>
         <v>11.182666666666668</v>
       </c>
-      <c r="S76" s="1">
-        <f t="shared" si="19"/>
-        <v>11.182666666666668</v>
-      </c>
       <c r="T76" s="1">
         <v>4.2</v>
       </c>
@@ -8879,7 +8911,7 @@
       </c>
       <c r="AB76" s="1"/>
       <c r="AC76" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AD76" s="1"/>
@@ -8905,10 +8937,10 @@
     </row>
     <row r="77" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C77" s="1">
         <v>40</v>
@@ -8927,32 +8959,32 @@
       </c>
       <c r="H77" s="1"/>
       <c r="I77" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="J77" s="1"/>
       <c r="K77" s="1">
         <v>31</v>
       </c>
       <c r="L77" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>2</v>
       </c>
       <c r="M77" s="1"/>
       <c r="N77" s="1"/>
       <c r="O77" s="1"/>
       <c r="P77" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>6.6</v>
       </c>
       <c r="Q77" s="5"/>
       <c r="R77" s="1">
+        <f t="shared" si="17"/>
+        <v>14.696969696969697</v>
+      </c>
+      <c r="S77" s="1">
         <f t="shared" si="18"/>
         <v>14.696969696969697</v>
       </c>
-      <c r="S77" s="1">
-        <f t="shared" si="19"/>
-        <v>14.696969696969697</v>
-      </c>
       <c r="T77" s="1">
         <v>7.4</v>
       </c>
@@ -8979,7 +9011,7 @@
       </c>
       <c r="AB77" s="1"/>
       <c r="AC77" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AD77" s="1"/>
@@ -9005,10 +9037,10 @@
     </row>
     <row r="78" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C78" s="1">
         <v>283</v>
@@ -9027,14 +9059,14 @@
       </c>
       <c r="H78" s="1"/>
       <c r="I78" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J78" s="1"/>
       <c r="K78" s="1">
         <v>109</v>
       </c>
       <c r="L78" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>4</v>
       </c>
       <c r="M78" s="1"/>
@@ -9043,18 +9075,18 @@
         <v>294.59999999999991</v>
       </c>
       <c r="P78" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>22.6</v>
       </c>
       <c r="Q78" s="5"/>
       <c r="R78" s="1">
+        <f t="shared" si="17"/>
+        <v>20.999999999999993</v>
+      </c>
+      <c r="S78" s="1">
         <f t="shared" si="18"/>
         <v>20.999999999999993</v>
       </c>
-      <c r="S78" s="1">
-        <f t="shared" si="19"/>
-        <v>20.999999999999993</v>
-      </c>
       <c r="T78" s="1">
         <v>44.8</v>
       </c>
@@ -9081,7 +9113,7 @@
       </c>
       <c r="AB78" s="1"/>
       <c r="AC78" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AD78" s="1"/>
@@ -9107,10 +9139,10 @@
     </row>
     <row r="79" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C79" s="1">
         <v>363.72300000000001</v>
@@ -9129,32 +9161,32 @@
       </c>
       <c r="H79" s="1"/>
       <c r="I79" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="J79" s="1"/>
       <c r="K79" s="1">
         <v>183.4</v>
       </c>
       <c r="L79" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>15.10299999999998</v>
       </c>
       <c r="M79" s="1"/>
       <c r="N79" s="1"/>
       <c r="O79" s="1"/>
       <c r="P79" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>39.700599999999994</v>
       </c>
       <c r="Q79" s="5"/>
       <c r="R79" s="1">
+        <f t="shared" si="17"/>
+        <v>23.930872581270815</v>
+      </c>
+      <c r="S79" s="1">
         <f t="shared" si="18"/>
         <v>23.930872581270815</v>
       </c>
-      <c r="S79" s="1">
-        <f t="shared" si="19"/>
-        <v>23.930872581270815</v>
-      </c>
       <c r="T79" s="1">
         <v>34.451799999999999</v>
       </c>
@@ -9180,10 +9212,10 @@
         <v>42.633200000000002</v>
       </c>
       <c r="AB79" s="17" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AC79" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AD79" s="1"/>
@@ -9209,10 +9241,10 @@
     </row>
     <row r="80" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C80" s="1">
         <v>1925.856</v>
@@ -9231,33 +9263,33 @@
       </c>
       <c r="H80" s="1"/>
       <c r="I80" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="J80" s="1"/>
       <c r="K80" s="1">
         <v>1572.7909999999999</v>
       </c>
       <c r="L80" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>28.619000000000142</v>
       </c>
       <c r="M80" s="1"/>
       <c r="N80" s="1"/>
       <c r="O80" s="1"/>
       <c r="P80" s="1">
+        <f t="shared" si="16"/>
+        <v>320.28200000000004</v>
+      </c>
+      <c r="Q80" s="18">
+        <f t="shared" ref="Q80:Q82" si="20">$Q$1*P80-O80-F80</f>
+        <v>771.6880000000001</v>
+      </c>
+      <c r="R80" s="1">
         <f t="shared" si="17"/>
-        <v>320.28200000000004</v>
-      </c>
-      <c r="Q80" s="5">
-        <f t="shared" si="9"/>
-        <v>131.12400000000025</v>
-      </c>
-      <c r="R80" s="1">
+        <v>12.999999999999998</v>
+      </c>
+      <c r="S80" s="1">
         <f t="shared" si="18"/>
-        <v>11</v>
-      </c>
-      <c r="S80" s="1">
-        <f t="shared" si="19"/>
         <v>10.590598285261112</v>
       </c>
       <c r="T80" s="1">
@@ -9286,8 +9318,8 @@
       </c>
       <c r="AB80" s="1"/>
       <c r="AC80" s="1">
-        <f t="shared" si="15"/>
-        <v>131.12400000000025</v>
+        <f t="shared" si="19"/>
+        <v>772</v>
       </c>
       <c r="AD80" s="1"/>
       <c r="AE80" s="1"/>
@@ -9312,10 +9344,10 @@
     </row>
     <row r="81" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C81" s="1">
         <v>1417.4</v>
@@ -9334,32 +9366,35 @@
       </c>
       <c r="H81" s="1"/>
       <c r="I81" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J81" s="1"/>
       <c r="K81" s="1">
         <v>1309.184</v>
       </c>
       <c r="L81" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>23.520999999999958</v>
       </c>
       <c r="M81" s="1"/>
       <c r="N81" s="1"/>
       <c r="O81" s="1"/>
       <c r="P81" s="1">
+        <f t="shared" si="16"/>
+        <v>266.541</v>
+      </c>
+      <c r="Q81" s="18">
+        <f t="shared" si="20"/>
+        <v>299.64300000000003</v>
+      </c>
+      <c r="R81" s="1">
         <f t="shared" si="17"/>
-        <v>266.541</v>
-      </c>
-      <c r="Q81" s="5"/>
-      <c r="R81" s="1">
+        <v>13</v>
+      </c>
+      <c r="S81" s="1">
         <f t="shared" si="18"/>
         <v>11.875808974979458</v>
       </c>
-      <c r="S81" s="1">
-        <f t="shared" si="19"/>
-        <v>11.875808974979458</v>
-      </c>
       <c r="T81" s="1">
         <v>299.10000000000002</v>
       </c>
@@ -9386,8 +9421,8 @@
       </c>
       <c r="AB81" s="1"/>
       <c r="AC81" s="1">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f t="shared" si="19"/>
+        <v>300</v>
       </c>
       <c r="AD81" s="1"/>
       <c r="AE81" s="1"/>
@@ -9412,10 +9447,10 @@
     </row>
     <row r="82" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C82" s="1">
         <v>2921.2089999999998</v>
@@ -9435,33 +9470,33 @@
       </c>
       <c r="H82" s="1"/>
       <c r="I82" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="J82" s="1"/>
       <c r="K82" s="1">
         <v>1881.306</v>
       </c>
       <c r="L82" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>25.589999999999918</v>
       </c>
       <c r="M82" s="1"/>
       <c r="N82" s="1"/>
       <c r="O82" s="1"/>
       <c r="P82" s="1">
+        <f t="shared" si="16"/>
+        <v>381.37919999999997</v>
+      </c>
+      <c r="Q82" s="18">
+        <f t="shared" si="20"/>
+        <v>872.75759999999946</v>
+      </c>
+      <c r="R82" s="1">
         <f t="shared" si="17"/>
-        <v>381.37919999999997</v>
-      </c>
-      <c r="Q82" s="5">
-        <f t="shared" si="9"/>
-        <v>109.99919999999975</v>
-      </c>
-      <c r="R82" s="1">
+        <v>13</v>
+      </c>
+      <c r="S82" s="1">
         <f t="shared" si="18"/>
-        <v>11</v>
-      </c>
-      <c r="S82" s="1">
-        <f t="shared" si="19"/>
         <v>10.71157525108868</v>
       </c>
       <c r="T82" s="1">
@@ -9490,8 +9525,8 @@
       </c>
       <c r="AB82" s="1"/>
       <c r="AC82" s="1">
-        <f t="shared" si="15"/>
-        <v>109.99919999999975</v>
+        <f t="shared" si="19"/>
+        <v>873</v>
       </c>
       <c r="AD82" s="1"/>
       <c r="AE82" s="1"/>
@@ -9516,10 +9551,10 @@
     </row>
     <row r="83" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C83" s="1">
         <v>130</v>
@@ -9538,33 +9573,33 @@
       </c>
       <c r="H83" s="1"/>
       <c r="I83" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J83" s="1"/>
       <c r="K83" s="1">
         <v>148</v>
       </c>
       <c r="L83" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>-8</v>
       </c>
       <c r="M83" s="1"/>
       <c r="N83" s="1"/>
       <c r="O83" s="1"/>
       <c r="P83" s="1">
+        <f t="shared" si="16"/>
+        <v>28</v>
+      </c>
+      <c r="Q83" s="5">
+        <f t="shared" si="8"/>
+        <v>182</v>
+      </c>
+      <c r="R83" s="1">
         <f t="shared" si="17"/>
-        <v>28</v>
-      </c>
-      <c r="Q83" s="5">
-        <f t="shared" si="9"/>
-        <v>182</v>
-      </c>
-      <c r="R83" s="1">
+        <v>11</v>
+      </c>
+      <c r="S83" s="1">
         <f t="shared" si="18"/>
-        <v>11</v>
-      </c>
-      <c r="S83" s="1">
-        <f t="shared" si="19"/>
         <v>4.5</v>
       </c>
       <c r="T83" s="1">
@@ -9593,8 +9628,8 @@
       </c>
       <c r="AB83" s="1"/>
       <c r="AC83" s="1">
-        <f t="shared" si="15"/>
-        <v>54.6</v>
+        <f t="shared" si="19"/>
+        <v>55</v>
       </c>
       <c r="AD83" s="1"/>
       <c r="AE83" s="1"/>
@@ -9619,10 +9654,10 @@
     </row>
     <row r="84" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C84" s="1">
         <v>136</v>
@@ -9641,32 +9676,32 @@
       </c>
       <c r="H84" s="1"/>
       <c r="I84" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="J84" s="1"/>
       <c r="K84" s="1">
         <v>77</v>
       </c>
       <c r="L84" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>-3</v>
       </c>
       <c r="M84" s="1"/>
       <c r="N84" s="1"/>
       <c r="O84" s="1"/>
       <c r="P84" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>14.8</v>
       </c>
       <c r="Q84" s="5"/>
       <c r="R84" s="1">
+        <f t="shared" si="17"/>
+        <v>13.445945945945946</v>
+      </c>
+      <c r="S84" s="1">
         <f t="shared" si="18"/>
         <v>13.445945945945946</v>
       </c>
-      <c r="S84" s="1">
-        <f t="shared" si="19"/>
-        <v>13.445945945945946</v>
-      </c>
       <c r="T84" s="1">
         <v>11.8</v>
       </c>
@@ -9693,7 +9728,7 @@
       </c>
       <c r="AB84" s="1"/>
       <c r="AC84" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AD84" s="1"/>
@@ -9719,10 +9754,10 @@
     </row>
     <row r="85" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C85" s="1">
         <v>176</v>
@@ -9741,33 +9776,33 @@
       </c>
       <c r="H85" s="1"/>
       <c r="I85" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J85" s="1"/>
       <c r="K85" s="1">
         <v>76</v>
       </c>
       <c r="L85" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>4</v>
       </c>
       <c r="M85" s="1"/>
       <c r="N85" s="1"/>
       <c r="O85" s="1"/>
       <c r="P85" s="1">
+        <f t="shared" si="16"/>
+        <v>16</v>
+      </c>
+      <c r="Q85" s="5">
+        <f t="shared" si="8"/>
+        <v>37</v>
+      </c>
+      <c r="R85" s="1">
         <f t="shared" si="17"/>
-        <v>16</v>
-      </c>
-      <c r="Q85" s="5">
-        <f t="shared" si="9"/>
-        <v>37</v>
-      </c>
-      <c r="R85" s="1">
+        <v>11</v>
+      </c>
+      <c r="S85" s="1">
         <f t="shared" si="18"/>
-        <v>11</v>
-      </c>
-      <c r="S85" s="1">
-        <f t="shared" si="19"/>
         <v>8.6875</v>
       </c>
       <c r="T85" s="1">
@@ -9796,8 +9831,8 @@
       </c>
       <c r="AB85" s="1"/>
       <c r="AC85" s="1">
-        <f t="shared" si="15"/>
-        <v>2.5900000000000003</v>
+        <f t="shared" si="19"/>
+        <v>3</v>
       </c>
       <c r="AD85" s="1"/>
       <c r="AE85" s="1"/>
@@ -9822,10 +9857,10 @@
     </row>
     <row r="86" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C86" s="1">
         <v>133</v>
@@ -9844,32 +9879,32 @@
       </c>
       <c r="H86" s="1"/>
       <c r="I86" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J86" s="1"/>
       <c r="K86" s="1">
         <v>69</v>
       </c>
       <c r="L86" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="M86" s="1"/>
       <c r="N86" s="1"/>
       <c r="O86" s="1"/>
       <c r="P86" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>13.8</v>
       </c>
       <c r="Q86" s="5"/>
       <c r="R86" s="1">
+        <f t="shared" si="17"/>
+        <v>12.318840579710145</v>
+      </c>
+      <c r="S86" s="1">
         <f t="shared" si="18"/>
         <v>12.318840579710145</v>
       </c>
-      <c r="S86" s="1">
-        <f t="shared" si="19"/>
-        <v>12.318840579710145</v>
-      </c>
       <c r="T86" s="1">
         <v>10</v>
       </c>
@@ -9896,7 +9931,7 @@
       </c>
       <c r="AB86" s="1"/>
       <c r="AC86" s="1">
-        <f t="shared" ref="AC86:AC114" si="20">G86*Q86</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AD86" s="1"/>
@@ -9922,10 +9957,10 @@
     </row>
     <row r="87" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C87" s="1">
         <v>154</v>
@@ -9944,14 +9979,14 @@
       </c>
       <c r="H87" s="1"/>
       <c r="I87" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="J87" s="1"/>
       <c r="K87" s="1">
         <v>78</v>
       </c>
       <c r="L87" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="M87" s="1"/>
@@ -9960,7 +9995,7 @@
         <v>15.80000000000001</v>
       </c>
       <c r="P87" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>15.6</v>
       </c>
       <c r="Q87" s="5">
@@ -9968,11 +10003,11 @@
         <v>30.799999999999983</v>
       </c>
       <c r="R87" s="1">
+        <f t="shared" si="17"/>
+        <v>11</v>
+      </c>
+      <c r="S87" s="1">
         <f t="shared" si="18"/>
-        <v>11</v>
-      </c>
-      <c r="S87" s="1">
-        <f t="shared" si="19"/>
         <v>9.0256410256410273</v>
       </c>
       <c r="T87" s="1">
@@ -10001,8 +10036,8 @@
       </c>
       <c r="AB87" s="1"/>
       <c r="AC87" s="1">
-        <f t="shared" si="20"/>
-        <v>1.5399999999999991</v>
+        <f t="shared" si="19"/>
+        <v>2</v>
       </c>
       <c r="AD87" s="1"/>
       <c r="AE87" s="1"/>
@@ -10027,10 +10062,10 @@
     </row>
     <row r="88" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A88" s="12" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B88" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C88" s="12"/>
       <c r="D88" s="12"/>
@@ -10041,14 +10076,14 @@
       </c>
       <c r="H88" s="12"/>
       <c r="I88" s="12" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="J88" s="12"/>
       <c r="K88" s="12">
         <v>7</v>
       </c>
       <c r="L88" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>-7</v>
       </c>
       <c r="M88" s="12"/>
@@ -10057,18 +10092,18 @@
         <v>0</v>
       </c>
       <c r="P88" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="Q88" s="14"/>
       <c r="R88" s="12" t="e">
+        <f t="shared" si="17"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S88" s="12" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S88" s="12" t="e">
-        <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
-      </c>
       <c r="T88" s="12">
         <v>3.4</v>
       </c>
@@ -10094,10 +10129,10 @@
         <v>13.6</v>
       </c>
       <c r="AB88" s="12" t="s">
-        <v>203</v>
-      </c>
-      <c r="AC88" s="12">
-        <f t="shared" si="20"/>
+        <v>202</v>
+      </c>
+      <c r="AC88" s="1">
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AD88" s="1"/>
@@ -10123,10 +10158,10 @@
     </row>
     <row r="89" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A89" s="12" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B89" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C89" s="12">
         <v>85</v>
@@ -10145,14 +10180,14 @@
       </c>
       <c r="H89" s="12"/>
       <c r="I89" s="12" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J89" s="12"/>
       <c r="K89" s="12">
         <v>57</v>
       </c>
       <c r="L89" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>-1</v>
       </c>
       <c r="M89" s="12"/>
@@ -10161,18 +10196,18 @@
         <v>0</v>
       </c>
       <c r="P89" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>11.2</v>
       </c>
       <c r="Q89" s="14"/>
       <c r="R89" s="12">
+        <f t="shared" si="17"/>
+        <v>6.6964285714285721</v>
+      </c>
+      <c r="S89" s="12">
         <f t="shared" si="18"/>
         <v>6.6964285714285721</v>
       </c>
-      <c r="S89" s="12">
-        <f t="shared" si="19"/>
-        <v>6.6964285714285721</v>
-      </c>
       <c r="T89" s="12">
         <v>13.8</v>
       </c>
@@ -10198,10 +10233,10 @@
         <v>11.8</v>
       </c>
       <c r="AB89" s="12" t="s">
-        <v>203</v>
-      </c>
-      <c r="AC89" s="12">
-        <f t="shared" si="20"/>
+        <v>202</v>
+      </c>
+      <c r="AC89" s="1">
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AD89" s="1"/>
@@ -10227,10 +10262,10 @@
     </row>
     <row r="90" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C90" s="1">
         <v>149.20599999999999</v>
@@ -10247,32 +10282,32 @@
       </c>
       <c r="H90" s="1"/>
       <c r="I90" s="12" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="J90" s="1"/>
       <c r="K90" s="1">
         <v>19.5</v>
       </c>
       <c r="L90" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>4.4810000000000016</v>
       </c>
       <c r="M90" s="1"/>
       <c r="N90" s="1"/>
       <c r="O90" s="1"/>
       <c r="P90" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>4.7962000000000007</v>
       </c>
       <c r="Q90" s="5"/>
       <c r="R90" s="1">
+        <f t="shared" si="17"/>
+        <v>26.108168967098948</v>
+      </c>
+      <c r="S90" s="1">
         <f t="shared" si="18"/>
         <v>26.108168967098948</v>
       </c>
-      <c r="S90" s="1">
-        <f t="shared" si="19"/>
-        <v>26.108168967098948</v>
-      </c>
       <c r="T90" s="1">
         <v>8.3277999999999999</v>
       </c>
@@ -10298,10 +10333,10 @@
         <v>9.8138000000000005</v>
       </c>
       <c r="AB90" s="17" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AC90" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AD90" s="1"/>
@@ -10327,10 +10362,10 @@
     </row>
     <row r="91" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C91" s="1">
         <v>2</v>
@@ -10347,14 +10382,14 @@
       </c>
       <c r="H91" s="1"/>
       <c r="I91" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="J91" s="1"/>
       <c r="K91" s="1">
         <v>16</v>
       </c>
       <c r="L91" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>-17</v>
       </c>
       <c r="M91" s="1"/>
@@ -10363,18 +10398,18 @@
         <v>10</v>
       </c>
       <c r="P91" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>-0.2</v>
       </c>
       <c r="Q91" s="5"/>
       <c r="R91" s="1">
+        <f t="shared" si="17"/>
+        <v>-60</v>
+      </c>
+      <c r="S91" s="1">
         <f t="shared" si="18"/>
         <v>-60</v>
       </c>
-      <c r="S91" s="1">
-        <f t="shared" si="19"/>
-        <v>-60</v>
-      </c>
       <c r="T91" s="1">
         <v>-0.4</v>
       </c>
@@ -10401,7 +10436,7 @@
       </c>
       <c r="AB91" s="1"/>
       <c r="AC91" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AD91" s="1"/>
@@ -10427,10 +10462,10 @@
     </row>
     <row r="92" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C92" s="1">
         <v>184</v>
@@ -10449,14 +10484,14 @@
       </c>
       <c r="H92" s="1"/>
       <c r="I92" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J92" s="1"/>
       <c r="K92" s="1">
         <v>122</v>
       </c>
       <c r="L92" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>-7</v>
       </c>
       <c r="M92" s="1"/>
@@ -10465,7 +10500,7 @@
         <v>120</v>
       </c>
       <c r="P92" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>23</v>
       </c>
       <c r="Q92" s="5">
@@ -10473,11 +10508,11 @@
         <v>32</v>
       </c>
       <c r="R92" s="1">
+        <f t="shared" si="17"/>
+        <v>11</v>
+      </c>
+      <c r="S92" s="1">
         <f t="shared" si="18"/>
-        <v>11</v>
-      </c>
-      <c r="S92" s="1">
-        <f t="shared" si="19"/>
         <v>9.6086956521739122</v>
       </c>
       <c r="T92" s="1">
@@ -10506,8 +10541,8 @@
       </c>
       <c r="AB92" s="1"/>
       <c r="AC92" s="1">
-        <f t="shared" si="20"/>
-        <v>2.56</v>
+        <f t="shared" si="19"/>
+        <v>3</v>
       </c>
       <c r="AD92" s="1"/>
       <c r="AE92" s="1"/>
@@ -10532,10 +10567,10 @@
     </row>
     <row r="93" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C93" s="1">
         <v>66</v>
@@ -10554,14 +10589,14 @@
       </c>
       <c r="H93" s="1"/>
       <c r="I93" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J93" s="1"/>
       <c r="K93" s="1">
         <v>80</v>
       </c>
       <c r="L93" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="M93" s="1"/>
@@ -10570,18 +10605,18 @@
         <v>76.998000000000019</v>
       </c>
       <c r="P93" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>16.2</v>
       </c>
       <c r="Q93" s="5"/>
       <c r="R93" s="1">
+        <f t="shared" si="17"/>
+        <v>11.85172839506173</v>
+      </c>
+      <c r="S93" s="1">
         <f t="shared" si="18"/>
         <v>11.85172839506173</v>
       </c>
-      <c r="S93" s="1">
-        <f t="shared" si="19"/>
-        <v>11.85172839506173</v>
-      </c>
       <c r="T93" s="1">
         <v>19.399999999999999</v>
       </c>
@@ -10608,7 +10643,7 @@
       </c>
       <c r="AB93" s="1"/>
       <c r="AC93" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AD93" s="1"/>
@@ -10634,10 +10669,10 @@
     </row>
     <row r="94" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C94" s="1">
         <v>3</v>
@@ -10652,14 +10687,14 @@
       </c>
       <c r="H94" s="1"/>
       <c r="I94" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J94" s="1"/>
       <c r="K94" s="1">
         <v>11</v>
       </c>
       <c r="L94" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>-11</v>
       </c>
       <c r="M94" s="1"/>
@@ -10668,18 +10703,18 @@
         <v>10</v>
       </c>
       <c r="P94" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="Q94" s="5"/>
       <c r="R94" s="1" t="e">
+        <f t="shared" si="17"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S94" s="1" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S94" s="1" t="e">
-        <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
-      </c>
       <c r="T94" s="1">
         <v>0</v>
       </c>
@@ -10706,7 +10741,7 @@
       </c>
       <c r="AB94" s="1"/>
       <c r="AC94" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AD94" s="1"/>
@@ -10732,10 +10767,10 @@
     </row>
     <row r="95" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C95" s="1">
         <v>187.07300000000001</v>
@@ -10754,14 +10789,14 @@
       </c>
       <c r="H95" s="1"/>
       <c r="I95" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="J95" s="1"/>
       <c r="K95" s="1">
         <v>197.02099999999999</v>
       </c>
       <c r="L95" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>-24.443999999999988</v>
       </c>
       <c r="M95" s="1"/>
@@ -10770,7 +10805,7 @@
         <v>57.318799999999939</v>
       </c>
       <c r="P95" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>34.5154</v>
       </c>
       <c r="Q95" s="5">
@@ -10778,11 +10813,11 @@
         <v>108.47460000000004</v>
       </c>
       <c r="R95" s="1">
+        <f t="shared" si="17"/>
+        <v>11</v>
+      </c>
+      <c r="S95" s="1">
         <f t="shared" si="18"/>
-        <v>11</v>
-      </c>
-      <c r="S95" s="1">
-        <f t="shared" si="19"/>
         <v>7.8572115635339568</v>
       </c>
       <c r="T95" s="1">
@@ -10811,8 +10846,8 @@
       </c>
       <c r="AB95" s="1"/>
       <c r="AC95" s="1">
-        <f t="shared" si="20"/>
-        <v>108.47460000000004</v>
+        <f t="shared" si="19"/>
+        <v>108</v>
       </c>
       <c r="AD95" s="1"/>
       <c r="AE95" s="1"/>
@@ -10837,10 +10872,10 @@
     </row>
     <row r="96" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C96" s="1">
         <v>450.65300000000002</v>
@@ -10859,32 +10894,32 @@
       </c>
       <c r="H96" s="1"/>
       <c r="I96" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="J96" s="1"/>
       <c r="K96" s="1">
         <v>128.19999999999999</v>
       </c>
       <c r="L96" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>-10.893999999999991</v>
       </c>
       <c r="M96" s="1"/>
       <c r="N96" s="1"/>
       <c r="O96" s="1"/>
       <c r="P96" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>23.461199999999998</v>
       </c>
       <c r="Q96" s="5"/>
       <c r="R96" s="1">
+        <f t="shared" si="17"/>
+        <v>18.143828960155492</v>
+      </c>
+      <c r="S96" s="1">
         <f t="shared" si="18"/>
         <v>18.143828960155492</v>
       </c>
-      <c r="S96" s="1">
-        <f t="shared" si="19"/>
-        <v>18.143828960155492</v>
-      </c>
       <c r="T96" s="1">
         <v>22.640799999999999</v>
       </c>
@@ -10910,10 +10945,10 @@
         <v>22.7972</v>
       </c>
       <c r="AB96" s="16" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AC96" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AD96" s="1"/>
@@ -10939,10 +10974,10 @@
     </row>
     <row r="97" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C97" s="1"/>
       <c r="D97" s="1">
@@ -10959,32 +10994,32 @@
       </c>
       <c r="H97" s="1"/>
       <c r="I97" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="J97" s="1"/>
       <c r="K97" s="1">
         <v>37.9</v>
       </c>
       <c r="L97" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>-3.7269999999999968</v>
       </c>
       <c r="M97" s="1"/>
       <c r="N97" s="1"/>
       <c r="O97" s="1"/>
       <c r="P97" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>6.8346</v>
       </c>
       <c r="Q97" s="5"/>
       <c r="R97" s="1">
+        <f t="shared" si="17"/>
+        <v>30.630761127205687</v>
+      </c>
+      <c r="S97" s="1">
         <f t="shared" si="18"/>
         <v>30.630761127205687</v>
       </c>
-      <c r="S97" s="1">
-        <f t="shared" si="19"/>
-        <v>30.630761127205687</v>
-      </c>
       <c r="T97" s="1">
         <v>-0.71160000000000001</v>
       </c>
@@ -11011,7 +11046,7 @@
       </c>
       <c r="AB97" s="1"/>
       <c r="AC97" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AD97" s="1"/>
@@ -11037,10 +11072,10 @@
     </row>
     <row r="98" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C98" s="1">
         <v>288</v>
@@ -11059,32 +11094,32 @@
       </c>
       <c r="H98" s="1"/>
       <c r="I98" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="J98" s="1"/>
       <c r="K98" s="1">
         <v>263</v>
       </c>
       <c r="L98" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>-19</v>
       </c>
       <c r="M98" s="1"/>
       <c r="N98" s="1"/>
       <c r="O98" s="1"/>
       <c r="P98" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>48.8</v>
       </c>
       <c r="Q98" s="5"/>
       <c r="R98" s="1">
+        <f t="shared" si="17"/>
+        <v>20.184426229508198</v>
+      </c>
+      <c r="S98" s="1">
         <f t="shared" si="18"/>
         <v>20.184426229508198</v>
       </c>
-      <c r="S98" s="1">
-        <f t="shared" si="19"/>
-        <v>20.184426229508198</v>
-      </c>
       <c r="T98" s="1">
         <v>37.4</v>
       </c>
@@ -11110,10 +11145,10 @@
         <v>45.2</v>
       </c>
       <c r="AB98" s="16" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AC98" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AD98" s="1"/>
@@ -11139,10 +11174,10 @@
     </row>
     <row r="99" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C99" s="1">
         <v>200</v>
@@ -11161,14 +11196,14 @@
       </c>
       <c r="H99" s="1"/>
       <c r="I99" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J99" s="1"/>
       <c r="K99" s="1">
         <v>214</v>
       </c>
       <c r="L99" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>-18</v>
       </c>
       <c r="M99" s="1"/>
@@ -11177,7 +11212,7 @@
         <v>229.2</v>
       </c>
       <c r="P99" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>39.200000000000003</v>
       </c>
       <c r="Q99" s="5">
@@ -11185,11 +11220,11 @@
         <v>187.00000000000006</v>
       </c>
       <c r="R99" s="1">
+        <f t="shared" si="17"/>
+        <v>11</v>
+      </c>
+      <c r="S99" s="1">
         <f t="shared" si="18"/>
-        <v>11</v>
-      </c>
-      <c r="S99" s="1">
-        <f t="shared" si="19"/>
         <v>6.2295918367346932</v>
       </c>
       <c r="T99" s="1">
@@ -11218,8 +11253,8 @@
       </c>
       <c r="AB99" s="1"/>
       <c r="AC99" s="1">
-        <f t="shared" si="20"/>
-        <v>52.360000000000021</v>
+        <f t="shared" si="19"/>
+        <v>52</v>
       </c>
       <c r="AD99" s="1"/>
       <c r="AE99" s="1"/>
@@ -11244,10 +11279,10 @@
     </row>
     <row r="100" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C100" s="1">
         <v>143</v>
@@ -11266,32 +11301,32 @@
       </c>
       <c r="H100" s="1"/>
       <c r="I100" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="J100" s="1"/>
       <c r="K100" s="1">
         <v>227</v>
       </c>
       <c r="L100" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>-48</v>
       </c>
       <c r="M100" s="1"/>
       <c r="N100" s="1"/>
       <c r="O100" s="1"/>
       <c r="P100" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>35.799999999999997</v>
       </c>
       <c r="Q100" s="5"/>
       <c r="R100" s="1">
+        <f t="shared" si="17"/>
+        <v>22.932960893854752</v>
+      </c>
+      <c r="S100" s="1">
         <f t="shared" si="18"/>
         <v>22.932960893854752</v>
       </c>
-      <c r="S100" s="1">
-        <f t="shared" si="19"/>
-        <v>22.932960893854752</v>
-      </c>
       <c r="T100" s="1">
         <v>46</v>
       </c>
@@ -11318,7 +11353,7 @@
       </c>
       <c r="AB100" s="1"/>
       <c r="AC100" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AD100" s="1"/>
@@ -11344,10 +11379,10 @@
     </row>
     <row r="101" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C101" s="1">
         <v>50</v>
@@ -11364,14 +11399,14 @@
       </c>
       <c r="H101" s="1"/>
       <c r="I101" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="J101" s="1"/>
       <c r="K101" s="1">
         <v>24</v>
       </c>
       <c r="L101" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>4</v>
       </c>
       <c r="M101" s="1"/>
@@ -11380,18 +11415,18 @@
         <v>48.800000000000011</v>
       </c>
       <c r="P101" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>5.6</v>
       </c>
       <c r="Q101" s="5"/>
       <c r="R101" s="1">
+        <f t="shared" si="17"/>
+        <v>12.642857142857146</v>
+      </c>
+      <c r="S101" s="1">
         <f t="shared" si="18"/>
         <v>12.642857142857146</v>
       </c>
-      <c r="S101" s="1">
-        <f t="shared" si="19"/>
-        <v>12.642857142857146</v>
-      </c>
       <c r="T101" s="1">
         <v>6.4</v>
       </c>
@@ -11417,10 +11452,10 @@
         <v>0</v>
       </c>
       <c r="AB101" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AC101" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AD101" s="1"/>
@@ -11446,10 +11481,10 @@
     </row>
     <row r="102" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C102" s="1">
         <v>262.39400000000001</v>
@@ -11468,7 +11503,7 @@
       </c>
       <c r="H102" s="1"/>
       <c r="I102" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J102" s="1"/>
       <c r="K102" s="1">
@@ -11523,8 +11558,8 @@
       </c>
       <c r="AB102" s="1"/>
       <c r="AC102" s="1">
-        <f t="shared" si="20"/>
-        <v>13.326600000000013</v>
+        <f t="shared" si="19"/>
+        <v>13</v>
       </c>
       <c r="AD102" s="1"/>
       <c r="AE102" s="1"/>
@@ -11549,10 +11584,10 @@
     </row>
     <row r="103" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C103" s="1">
         <v>113.247</v>
@@ -11571,7 +11606,7 @@
       </c>
       <c r="H103" s="1"/>
       <c r="I103" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J103" s="1"/>
       <c r="K103" s="1">
@@ -11623,7 +11658,7 @@
       </c>
       <c r="AB103" s="1"/>
       <c r="AC103" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AD103" s="1"/>
@@ -11649,10 +11684,10 @@
     </row>
     <row r="104" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C104" s="1">
         <v>50</v>
@@ -11671,7 +11706,7 @@
       </c>
       <c r="H104" s="1"/>
       <c r="I104" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J104" s="1"/>
       <c r="K104" s="1">
@@ -11724,10 +11759,10 @@
         <v>0</v>
       </c>
       <c r="AB104" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AC104" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AD104" s="1"/>
@@ -11753,10 +11788,10 @@
     </row>
     <row r="105" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C105" s="1">
         <v>50</v>
@@ -11775,7 +11810,7 @@
       </c>
       <c r="H105" s="1"/>
       <c r="I105" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="J105" s="1"/>
       <c r="K105" s="1">
@@ -11828,10 +11863,10 @@
         <v>0</v>
       </c>
       <c r="AB105" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AC105" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AD105" s="1"/>
@@ -11857,10 +11892,10 @@
     </row>
     <row r="106" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C106" s="1">
         <v>327.40499999999997</v>
@@ -11879,7 +11914,7 @@
       </c>
       <c r="H106" s="1"/>
       <c r="I106" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="J106" s="1"/>
       <c r="K106" s="1">
@@ -11930,10 +11965,10 @@
         <v>14.403</v>
       </c>
       <c r="AB106" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AC106" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AD106" s="1"/>
@@ -11959,10 +11994,10 @@
     </row>
     <row r="107" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C107" s="1">
         <v>319.28100000000001</v>
@@ -11981,7 +12016,7 @@
       </c>
       <c r="H107" s="1"/>
       <c r="I107" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J107" s="1"/>
       <c r="K107" s="1">
@@ -12032,10 +12067,10 @@
         <v>39.076000000000001</v>
       </c>
       <c r="AB107" s="16" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AC107" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AD107" s="1"/>
@@ -12061,10 +12096,10 @@
     </row>
     <row r="108" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C108" s="1">
         <v>121.90900000000001</v>
@@ -12083,7 +12118,7 @@
       </c>
       <c r="H108" s="1"/>
       <c r="I108" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="J108" s="1"/>
       <c r="K108" s="1">
@@ -12135,7 +12170,7 @@
       </c>
       <c r="AB108" s="1"/>
       <c r="AC108" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AD108" s="1"/>
@@ -12161,10 +12196,10 @@
     </row>
     <row r="109" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C109" s="1">
         <v>1963.347</v>
@@ -12234,10 +12269,10 @@
         <v>0</v>
       </c>
       <c r="AB109" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AC109" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AD109" s="1"/>
@@ -12263,10 +12298,10 @@
     </row>
     <row r="110" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C110" s="1">
         <v>266</v>
@@ -12285,7 +12320,7 @@
       </c>
       <c r="H110" s="1"/>
       <c r="I110" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="J110" s="1"/>
       <c r="K110" s="1">
@@ -12337,7 +12372,7 @@
       </c>
       <c r="AB110" s="1"/>
       <c r="AC110" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AD110" s="1"/>
@@ -12363,10 +12398,10 @@
     </row>
     <row r="111" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C111" s="1">
         <v>18</v>
@@ -12385,7 +12420,7 @@
       </c>
       <c r="H111" s="1"/>
       <c r="I111" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="J111" s="1"/>
       <c r="K111" s="1">
@@ -12437,7 +12472,7 @@
       </c>
       <c r="AB111" s="1"/>
       <c r="AC111" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AD111" s="1"/>
@@ -12463,10 +12498,10 @@
     </row>
     <row r="112" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C112" s="1">
         <v>53.963000000000001</v>
@@ -12485,7 +12520,7 @@
       </c>
       <c r="H112" s="1"/>
       <c r="I112" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J112" s="1"/>
       <c r="K112" s="1">
@@ -12536,10 +12571,10 @@
         <v>4.6696</v>
       </c>
       <c r="AB112" s="16" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AC112" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AD112" s="1"/>
@@ -12565,10 +12600,10 @@
     </row>
     <row r="113" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C113" s="1">
         <v>191</v>
@@ -12587,7 +12622,7 @@
       </c>
       <c r="H113" s="1"/>
       <c r="I113" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="J113" s="1"/>
       <c r="K113" s="1">
@@ -12644,8 +12679,8 @@
       </c>
       <c r="AB113" s="1"/>
       <c r="AC113" s="1">
-        <f t="shared" si="20"/>
-        <v>16.559999999999995</v>
+        <f t="shared" si="19"/>
+        <v>17</v>
       </c>
       <c r="AD113" s="1"/>
       <c r="AE113" s="1"/>
@@ -12670,10 +12705,10 @@
     </row>
     <row r="114" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C114" s="1">
         <v>42</v>
@@ -12692,7 +12727,7 @@
       </c>
       <c r="H114" s="1"/>
       <c r="I114" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="J114" s="1"/>
       <c r="K114" s="1">
@@ -12746,7 +12781,7 @@
       </c>
       <c r="AB114" s="1"/>
       <c r="AC114" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AD114" s="1"/>
